--- a/data/nzd0175/nzd0175.xlsx
+++ b/data/nzd0175/nzd0175.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U347"/>
+  <dimension ref="A1:U348"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24344,13 +24344,13 @@
         <v>298.48</v>
       </c>
       <c r="D347" t="n">
-        <v>294.21</v>
+        <v>295.88</v>
       </c>
       <c r="E347" t="n">
         <v>317.83</v>
       </c>
       <c r="F347" t="n">
-        <v>298.11</v>
+        <v>299.32</v>
       </c>
       <c r="G347" t="n">
         <v>297.65</v>
@@ -24397,6 +24397,75 @@
       <c r="U347" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-16 22:06:00+00:00</t>
+        </is>
+      </c>
+      <c r="B348" t="n">
+        <v>315.6</v>
+      </c>
+      <c r="C348" t="n">
+        <v>299.81</v>
+      </c>
+      <c r="D348" t="n">
+        <v>296.4</v>
+      </c>
+      <c r="E348" t="n">
+        <v>319.14</v>
+      </c>
+      <c r="F348" t="n">
+        <v>299.37</v>
+      </c>
+      <c r="G348" t="n">
+        <v>296.81</v>
+      </c>
+      <c r="H348" t="n">
+        <v>300.98</v>
+      </c>
+      <c r="I348" t="n">
+        <v>310.19</v>
+      </c>
+      <c r="J348" t="n">
+        <v>321.35</v>
+      </c>
+      <c r="K348" t="n">
+        <v>327.11</v>
+      </c>
+      <c r="L348" t="n">
+        <v>331.4</v>
+      </c>
+      <c r="M348" t="n">
+        <v>342.67</v>
+      </c>
+      <c r="N348" t="n">
+        <v>356.1</v>
+      </c>
+      <c r="O348" t="n">
+        <v>361.75</v>
+      </c>
+      <c r="P348" t="n">
+        <v>370.41</v>
+      </c>
+      <c r="Q348" t="n">
+        <v>371.66</v>
+      </c>
+      <c r="R348" t="n">
+        <v>378.63</v>
+      </c>
+      <c r="S348" t="n">
+        <v>378.33</v>
+      </c>
+      <c r="T348" t="n">
+        <v>367.91</v>
+      </c>
+      <c r="U348" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -24411,7 +24480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B357"/>
+  <dimension ref="A1:B358"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27984,6 +28053,16 @@
       </c>
       <c r="B357" t="n">
         <v>0.3</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>2025-12-16 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B358" t="n">
+        <v>-0.45</v>
       </c>
     </row>
   </sheetData>
@@ -28152,28 +28231,28 @@
         <v>0.1008</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3313178876978756</v>
+        <v>0.3327506128626054</v>
       </c>
       <c r="J2" t="n">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="K2" t="n">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1529429601833345</v>
+        <v>0.1548193463260867</v>
       </c>
       <c r="M2" t="n">
-        <v>4.341180386081319</v>
+        <v>4.335082033128856</v>
       </c>
       <c r="N2" t="n">
-        <v>32.26149857954588</v>
+        <v>32.18577274830102</v>
       </c>
       <c r="O2" t="n">
-        <v>5.679920649053636</v>
+        <v>5.67325063330548</v>
       </c>
       <c r="P2" t="n">
-        <v>304.3856745624591</v>
+        <v>304.3703445818022</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -28230,28 +28309,28 @@
         <v>0.1504</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.07798139974061236</v>
+        <v>-0.07742107415303272</v>
       </c>
       <c r="J3" t="n">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="K3" t="n">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="L3" t="n">
-        <v>0.009598121907506862</v>
+        <v>0.009520631038513416</v>
       </c>
       <c r="M3" t="n">
-        <v>4.243026150261886</v>
+        <v>4.23340076279239</v>
       </c>
       <c r="N3" t="n">
-        <v>33.2980538187147</v>
+        <v>33.20473193985679</v>
       </c>
       <c r="O3" t="n">
-        <v>5.770446587458782</v>
+        <v>5.762354721800524</v>
       </c>
       <c r="P3" t="n">
-        <v>300.9087035484907</v>
+        <v>300.9027081345546</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -28308,28 +28387,28 @@
         <v>0.1503</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.05008437833129779</v>
+        <v>-0.05223006013175954</v>
       </c>
       <c r="J4" t="n">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="K4" t="n">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="L4" t="n">
-        <v>0.004640809362980614</v>
+        <v>0.005073659070544911</v>
       </c>
       <c r="M4" t="n">
-        <v>3.958531881206221</v>
+        <v>3.95835628098548</v>
       </c>
       <c r="N4" t="n">
-        <v>28.54974817144286</v>
+        <v>28.48476194274484</v>
       </c>
       <c r="O4" t="n">
-        <v>5.343196437661904</v>
+        <v>5.337111760376097</v>
       </c>
       <c r="P4" t="n">
-        <v>303.0514586065277</v>
+        <v>303.0744659549586</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -28386,28 +28465,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.05114576892865492</v>
+        <v>-0.04957380359805357</v>
       </c>
       <c r="J5" t="n">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="K5" t="n">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01069469136143064</v>
+        <v>0.01010075822844647</v>
       </c>
       <c r="M5" t="n">
-        <v>2.705782903049832</v>
+        <v>2.706221781485775</v>
       </c>
       <c r="N5" t="n">
-        <v>12.84083048548567</v>
+        <v>12.82458717042465</v>
       </c>
       <c r="O5" t="n">
-        <v>3.583410454509178</v>
+        <v>3.58114327700312</v>
       </c>
       <c r="P5" t="n">
-        <v>317.7995230241448</v>
+        <v>317.782703191071</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -28464,28 +28543,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>0.06012547710865792</v>
+        <v>0.05942665348373326</v>
       </c>
       <c r="J6" t="n">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="K6" t="n">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01119971493776339</v>
+        <v>0.01101532961172214</v>
       </c>
       <c r="M6" t="n">
-        <v>3.206953133333688</v>
+        <v>3.199974471985925</v>
       </c>
       <c r="N6" t="n">
-        <v>16.93675830285718</v>
+        <v>16.88326767776108</v>
       </c>
       <c r="O6" t="n">
-        <v>4.115429297516504</v>
+        <v>4.108925367752629</v>
       </c>
       <c r="P6" t="n">
-        <v>300.1760585194111</v>
+        <v>300.1835713180834</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -28542,28 +28621,28 @@
         <v>0.0881</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1153581567868148</v>
+        <v>0.1166676407860653</v>
       </c>
       <c r="J7" t="n">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="K7" t="n">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="L7" t="n">
-        <v>0.03000740181840689</v>
+        <v>0.03084097419034393</v>
       </c>
       <c r="M7" t="n">
-        <v>3.874331935918257</v>
+        <v>3.86955145609384</v>
       </c>
       <c r="N7" t="n">
-        <v>22.82696891926126</v>
+        <v>22.77559245439221</v>
       </c>
       <c r="O7" t="n">
-        <v>4.777757729234631</v>
+        <v>4.772378071191784</v>
       </c>
       <c r="P7" t="n">
-        <v>291.5132735314472</v>
+        <v>291.4992622158975</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -28620,28 +28699,28 @@
         <v>0.1029</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3462015268371229</v>
+        <v>0.3464618647631305</v>
       </c>
       <c r="J8" t="n">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="K8" t="n">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1614703824769962</v>
+        <v>0.1625297700815139</v>
       </c>
       <c r="M8" t="n">
-        <v>4.685288153610406</v>
+        <v>4.673188107048607</v>
       </c>
       <c r="N8" t="n">
-        <v>33.02897492215185</v>
+        <v>32.93436000862341</v>
       </c>
       <c r="O8" t="n">
-        <v>5.747084036461608</v>
+        <v>5.738846574759027</v>
       </c>
       <c r="P8" t="n">
-        <v>291.392874591669</v>
+        <v>291.3900890083148</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -28698,28 +28777,28 @@
         <v>0.1076</v>
       </c>
       <c r="I9" t="n">
-        <v>0.27470718926585</v>
+        <v>0.2763026481791255</v>
       </c>
       <c r="J9" t="n">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="K9" t="n">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1037237749252273</v>
+        <v>0.1053412449597914</v>
       </c>
       <c r="M9" t="n">
-        <v>4.807858898312512</v>
+        <v>4.801702009529238</v>
       </c>
       <c r="N9" t="n">
-        <v>34.60311670918299</v>
+        <v>34.52478309913319</v>
       </c>
       <c r="O9" t="n">
-        <v>5.882441390203815</v>
+        <v>5.875779360998266</v>
       </c>
       <c r="P9" t="n">
-        <v>300.1983160836079</v>
+        <v>300.1812448721282</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -28776,28 +28855,28 @@
         <v>0.1135</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1260601418660002</v>
+        <v>0.130386500394928</v>
       </c>
       <c r="J10" t="n">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="K10" t="n">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="L10" t="n">
-        <v>0.02806280967179065</v>
+        <v>0.02999047472372407</v>
       </c>
       <c r="M10" t="n">
-        <v>4.287730975501449</v>
+        <v>4.298759325542117</v>
       </c>
       <c r="N10" t="n">
-        <v>29.20614501591849</v>
+        <v>29.27924077079022</v>
       </c>
       <c r="O10" t="n">
-        <v>5.404270997638672</v>
+        <v>5.411029548135015</v>
       </c>
       <c r="P10" t="n">
-        <v>310.6031856814942</v>
+        <v>310.5568941845651</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -28854,28 +28933,28 @@
         <v>0.2</v>
       </c>
       <c r="I11" t="n">
-        <v>0.248538872088431</v>
+        <v>0.2511480214981631</v>
       </c>
       <c r="J11" t="n">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="K11" t="n">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1077375970450267</v>
+        <v>0.1101716496872542</v>
       </c>
       <c r="M11" t="n">
-        <v>3.891175900487249</v>
+        <v>3.892475317067451</v>
       </c>
       <c r="N11" t="n">
-        <v>27.26841901333037</v>
+        <v>27.24697215316252</v>
       </c>
       <c r="O11" t="n">
-        <v>5.221917177946273</v>
+        <v>5.219863231269811</v>
       </c>
       <c r="P11" t="n">
-        <v>316.0625569293595</v>
+        <v>316.0346677751571</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -28932,28 +29011,28 @@
         <v>0.1208</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1955940358523751</v>
+        <v>0.1968930474521778</v>
       </c>
       <c r="J12" t="n">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="K12" t="n">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="L12" t="n">
-        <v>0.05501051859448658</v>
+        <v>0.05601447607719101</v>
       </c>
       <c r="M12" t="n">
-        <v>4.647975656387441</v>
+        <v>4.640422103153087</v>
       </c>
       <c r="N12" t="n">
-        <v>34.87418409650506</v>
+        <v>34.78785991323053</v>
       </c>
       <c r="O12" t="n">
-        <v>5.905436825206503</v>
+        <v>5.898123423024525</v>
       </c>
       <c r="P12" t="n">
-        <v>324.009443034575</v>
+        <v>323.9955437723938</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -29010,28 +29089,28 @@
         <v>0.1693</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1802172983616757</v>
+        <v>0.182450571727717</v>
       </c>
       <c r="J13" t="n">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="K13" t="n">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="L13" t="n">
-        <v>0.05520112906892394</v>
+        <v>0.0567613920586435</v>
       </c>
       <c r="M13" t="n">
-        <v>4.158293901144188</v>
+        <v>4.155009167593581</v>
       </c>
       <c r="N13" t="n">
-        <v>29.49823011812407</v>
+        <v>29.45512584353215</v>
       </c>
       <c r="O13" t="n">
-        <v>5.431227312323069</v>
+        <v>5.427257672483604</v>
       </c>
       <c r="P13" t="n">
-        <v>334.0830239571265</v>
+        <v>334.0591282105131</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -29088,28 +29167,28 @@
         <v>0.2</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1400056749964367</v>
+        <v>0.1413254355992022</v>
       </c>
       <c r="J14" t="n">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="K14" t="n">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="L14" t="n">
-        <v>0.03778479932600654</v>
+        <v>0.03868675641961894</v>
       </c>
       <c r="M14" t="n">
-        <v>3.896408438747601</v>
+        <v>3.89001616533135</v>
       </c>
       <c r="N14" t="n">
-        <v>26.48853732140677</v>
+        <v>26.42683580563856</v>
       </c>
       <c r="O14" t="n">
-        <v>5.146701596304839</v>
+        <v>5.140703823956265</v>
       </c>
       <c r="P14" t="n">
-        <v>350.1364913721693</v>
+        <v>350.1223700982431</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -29166,28 +29245,28 @@
         <v>0.2</v>
       </c>
       <c r="I15" t="n">
-        <v>0.2195390895250851</v>
+        <v>0.2209338418021049</v>
       </c>
       <c r="J15" t="n">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="K15" t="n">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="L15" t="n">
-        <v>0.08157180013339638</v>
+        <v>0.08296204358221193</v>
       </c>
       <c r="M15" t="n">
-        <v>4.033843625746726</v>
+        <v>4.027734583623571</v>
       </c>
       <c r="N15" t="n">
-        <v>28.79655172177098</v>
+        <v>28.7299092270843</v>
       </c>
       <c r="O15" t="n">
-        <v>5.366241862026998</v>
+        <v>5.360028845732484</v>
       </c>
       <c r="P15" t="n">
-        <v>353.5584244675668</v>
+        <v>353.5435007920746</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -29244,28 +29323,28 @@
         <v>0.2</v>
       </c>
       <c r="I16" t="n">
-        <v>0.3093830613228906</v>
+        <v>0.310020714515874</v>
       </c>
       <c r="J16" t="n">
+        <v>347</v>
+      </c>
+      <c r="K16" t="n">
         <v>346</v>
       </c>
-      <c r="K16" t="n">
-        <v>345</v>
-      </c>
       <c r="L16" t="n">
-        <v>0.165902884665061</v>
+        <v>0.1673325463472415</v>
       </c>
       <c r="M16" t="n">
-        <v>3.942541302926948</v>
+        <v>3.933054378798797</v>
       </c>
       <c r="N16" t="n">
-        <v>25.52150373622762</v>
+        <v>25.4511590852525</v>
       </c>
       <c r="O16" t="n">
-        <v>5.051881207652019</v>
+        <v>5.044914180167241</v>
       </c>
       <c r="P16" t="n">
-        <v>361.1439524091899</v>
+        <v>361.1371196722387</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -29322,28 +29401,28 @@
         <v>0.2</v>
       </c>
       <c r="I17" t="n">
-        <v>0.3848281966492595</v>
+        <v>0.3846119102244674</v>
       </c>
       <c r="J17" t="n">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="K17" t="n">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="L17" t="n">
-        <v>0.2776052664508668</v>
+        <v>0.2786440293959017</v>
       </c>
       <c r="M17" t="n">
-        <v>3.488765890620394</v>
+        <v>3.479910734541329</v>
       </c>
       <c r="N17" t="n">
-        <v>20.44994979724602</v>
+        <v>20.3914092681424</v>
       </c>
       <c r="O17" t="n">
-        <v>4.522162071094535</v>
+        <v>4.515684806111073</v>
       </c>
       <c r="P17" t="n">
-        <v>361.8644259769108</v>
+        <v>361.8667402146934</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -29400,28 +29479,28 @@
         <v>0.2</v>
       </c>
       <c r="I18" t="n">
-        <v>0.2923299991807276</v>
+        <v>0.2951298288110557</v>
       </c>
       <c r="J18" t="n">
+        <v>347</v>
+      </c>
+      <c r="K18" t="n">
         <v>346</v>
       </c>
-      <c r="K18" t="n">
-        <v>345</v>
-      </c>
       <c r="L18" t="n">
-        <v>0.1146255396917322</v>
+        <v>0.1170361365411406</v>
       </c>
       <c r="M18" t="n">
-        <v>4.362673505496376</v>
+        <v>4.363178839161517</v>
       </c>
       <c r="N18" t="n">
-        <v>34.6609242647966</v>
+        <v>34.62559980716309</v>
       </c>
       <c r="O18" t="n">
-        <v>5.887352908124041</v>
+        <v>5.884352114478117</v>
       </c>
       <c r="P18" t="n">
-        <v>366.14927610829</v>
+        <v>366.119105058717</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -29478,28 +29557,28 @@
         <v>0.1952</v>
       </c>
       <c r="I19" t="n">
-        <v>0.3605465109371073</v>
+        <v>0.3637494568815251</v>
       </c>
       <c r="J19" t="n">
+        <v>347</v>
+      </c>
+      <c r="K19" t="n">
         <v>346</v>
       </c>
-      <c r="K19" t="n">
-        <v>345</v>
-      </c>
       <c r="L19" t="n">
-        <v>0.1669885006343992</v>
+        <v>0.1700064964125075</v>
       </c>
       <c r="M19" t="n">
-        <v>4.504736254826459</v>
+        <v>4.503215636595882</v>
       </c>
       <c r="N19" t="n">
-        <v>34.05138632131958</v>
+        <v>34.03784243020563</v>
       </c>
       <c r="O19" t="n">
-        <v>5.835356571908831</v>
+        <v>5.834195954045907</v>
       </c>
       <c r="P19" t="n">
-        <v>363.3664577558637</v>
+        <v>363.3319427125832</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -29556,28 +29635,28 @@
         <v>0.2</v>
       </c>
       <c r="I20" t="n">
-        <v>0.3227187269275362</v>
+        <v>0.3266556454704557</v>
       </c>
       <c r="J20" t="n">
+        <v>347</v>
+      </c>
+      <c r="K20" t="n">
         <v>346</v>
       </c>
-      <c r="K20" t="n">
-        <v>345</v>
-      </c>
       <c r="L20" t="n">
-        <v>0.1395998821488006</v>
+        <v>0.1428490939139171</v>
       </c>
       <c r="M20" t="n">
-        <v>4.528187173414719</v>
+        <v>4.534650619425588</v>
       </c>
       <c r="N20" t="n">
-        <v>33.70633376568903</v>
+        <v>33.73714096541792</v>
       </c>
       <c r="O20" t="n">
-        <v>5.805715611850879</v>
+        <v>5.808368184388617</v>
       </c>
       <c r="P20" t="n">
-        <v>352.6952750161398</v>
+        <v>352.6528506617302</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -29615,7 +29694,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U347"/>
+  <dimension ref="A1:U348"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -66634,7 +66713,7 @@
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>-36.79290694163823,175.72671689953083</t>
+          <t>-36.7929185101167,175.72672885668408</t>
         </is>
       </c>
       <c r="E347" t="inlineStr">
@@ -66644,7 +66723,7 @@
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>-36.794279783967085,175.72551546612664</t>
+          <t>-36.794283740806954,175.72552809442286</t>
         </is>
       </c>
       <c r="G347" t="inlineStr">
@@ -66720,6 +66799,113 @@
       <c r="U347" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-16 22:06:00+00:00</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>-36.792180934629584,175.72831380642276</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>-36.792503024766084,175.7274878924884</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>-36.79292211227739,175.72673257987026</t>
+        </is>
+      </c>
+      <c r="E348" t="inlineStr">
+        <is>
+          <t>-36.79360767187361,175.72613173053222</t>
+        </is>
+      </c>
+      <c r="F348" t="inlineStr">
+        <is>
+          <t>-36.794283904312714,175.72552861625329</t>
+        </is>
+      </c>
+      <c r="G348" t="inlineStr">
+        <is>
+          <t>-36.79494071173821,175.72515987411003</t>
+        </is>
+      </c>
+      <c r="H348" t="inlineStr">
+        <is>
+          <t>-36.795623852147784,175.72485915152973</t>
+        </is>
+      </c>
+      <c r="I348" t="inlineStr">
+        <is>
+          <t>-36.79632684183176,175.72462638068012</t>
+        </is>
+      </c>
+      <c r="J348" t="inlineStr">
+        <is>
+          <t>-36.797034360311905,175.72441489261385</t>
+        </is>
+      </c>
+      <c r="K348" t="inlineStr">
+        <is>
+          <t>-36.79773694213543,175.7241575916029</t>
+        </is>
+      </c>
+      <c r="L348" t="inlineStr">
+        <is>
+          <t>-36.79844485140648,175.72394048994167</t>
+        </is>
+      </c>
+      <c r="M348" t="inlineStr">
+        <is>
+          <t>-36.79916232882833,175.72380180275064</t>
+        </is>
+      </c>
+      <c r="N348" t="inlineStr">
+        <is>
+          <t>-36.79988840229049,175.7237013041795</t>
+        </is>
+      </c>
+      <c r="O348" t="inlineStr">
+        <is>
+          <t>-36.800611127352596,175.72366874611976</t>
+        </is>
+      </c>
+      <c r="P348" t="inlineStr">
+        <is>
+          <t>-36.80132659475955,175.72367093287767</t>
+        </is>
+      </c>
+      <c r="Q348" t="inlineStr">
+        <is>
+          <t>-36.80203731868134,175.72371821700884</t>
+        </is>
+      </c>
+      <c r="R348" t="inlineStr">
+        <is>
+          <t>-36.80274226909438,175.72383621436427</t>
+        </is>
+      </c>
+      <c r="S348" t="inlineStr">
+        <is>
+          <t>-36.803432052318264,175.72396794146084</t>
+        </is>
+      </c>
+      <c r="T348" t="inlineStr">
+        <is>
+          <t>-36.804145095789735,175.7240826015253</t>
+        </is>
+      </c>
+      <c r="U348" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>

--- a/data/nzd0175/nzd0175.xlsx
+++ b/data/nzd0175/nzd0175.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U348"/>
+  <dimension ref="A1:U349"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24466,6 +24466,75 @@
       <c r="U348" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-09 22:05:44+00:00</t>
+        </is>
+      </c>
+      <c r="B349" t="n">
+        <v>315.04</v>
+      </c>
+      <c r="C349" t="n">
+        <v>299.01</v>
+      </c>
+      <c r="D349" t="n">
+        <v>295.71</v>
+      </c>
+      <c r="E349" t="n">
+        <v>316.32</v>
+      </c>
+      <c r="F349" t="n">
+        <v>296.56</v>
+      </c>
+      <c r="G349" t="n">
+        <v>293.81</v>
+      </c>
+      <c r="H349" t="n">
+        <v>299.88</v>
+      </c>
+      <c r="I349" t="n">
+        <v>306.76</v>
+      </c>
+      <c r="J349" t="n">
+        <v>316.98</v>
+      </c>
+      <c r="K349" t="n">
+        <v>324.23</v>
+      </c>
+      <c r="L349" t="n">
+        <v>328.66</v>
+      </c>
+      <c r="M349" t="n">
+        <v>341.85</v>
+      </c>
+      <c r="N349" t="n">
+        <v>355.23</v>
+      </c>
+      <c r="O349" t="n">
+        <v>361.63</v>
+      </c>
+      <c r="P349" t="n">
+        <v>370.53</v>
+      </c>
+      <c r="Q349" t="n">
+        <v>371.51</v>
+      </c>
+      <c r="R349" t="n">
+        <v>376.65</v>
+      </c>
+      <c r="S349" t="n">
+        <v>377.11</v>
+      </c>
+      <c r="T349" t="n">
+        <v>365.1</v>
+      </c>
+      <c r="U349" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -24480,7 +24549,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B358"/>
+  <dimension ref="A1:B359"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28063,6 +28132,16 @@
       </c>
       <c r="B358" t="n">
         <v>-0.45</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>2026-01-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B359" t="n">
+        <v>0.52</v>
       </c>
     </row>
   </sheetData>
@@ -28231,28 +28310,28 @@
         <v>0.1008</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3327506128626054</v>
+        <v>0.3338276441849415</v>
       </c>
       <c r="J2" t="n">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="K2" t="n">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1548193463260867</v>
+        <v>0.1564589310362356</v>
       </c>
       <c r="M2" t="n">
-        <v>4.335082033128856</v>
+        <v>4.327408551104512</v>
       </c>
       <c r="N2" t="n">
-        <v>32.18577274830102</v>
+        <v>32.10306396555252</v>
       </c>
       <c r="O2" t="n">
-        <v>5.67325063330548</v>
+        <v>5.665956579921215</v>
       </c>
       <c r="P2" t="n">
-        <v>304.3703445818022</v>
+        <v>304.3587881992312</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -28309,28 +28388,28 @@
         <v>0.1504</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.07742107415303272</v>
+        <v>-0.0773295768358421</v>
       </c>
       <c r="J3" t="n">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="K3" t="n">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="L3" t="n">
-        <v>0.009520631038513416</v>
+        <v>0.009557960115817554</v>
       </c>
       <c r="M3" t="n">
-        <v>4.23340076279239</v>
+        <v>4.221657715779804</v>
       </c>
       <c r="N3" t="n">
-        <v>33.20473193985679</v>
+        <v>33.10938661956995</v>
       </c>
       <c r="O3" t="n">
-        <v>5.762354721800524</v>
+        <v>5.754075652923756</v>
       </c>
       <c r="P3" t="n">
-        <v>300.9027081345546</v>
+        <v>300.9017263822326</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -28387,28 +28466,28 @@
         <v>0.1503</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.05223006013175954</v>
+        <v>-0.05570618281974439</v>
       </c>
       <c r="J4" t="n">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="K4" t="n">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="L4" t="n">
-        <v>0.005073659070544911</v>
+        <v>0.005783174518133705</v>
       </c>
       <c r="M4" t="n">
-        <v>3.95835628098548</v>
+        <v>3.965316278058648</v>
       </c>
       <c r="N4" t="n">
-        <v>28.48476194274484</v>
+        <v>28.5047756068518</v>
       </c>
       <c r="O4" t="n">
-        <v>5.337111760376097</v>
+        <v>5.338986383842143</v>
       </c>
       <c r="P4" t="n">
-        <v>303.0744659549586</v>
+        <v>303.1117642236467</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -28465,28 +28544,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.04957380359805357</v>
+        <v>-0.04965998781471327</v>
       </c>
       <c r="J5" t="n">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="K5" t="n">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01010075822844647</v>
+        <v>0.01019908782579149</v>
       </c>
       <c r="M5" t="n">
-        <v>2.706221781485775</v>
+        <v>2.698833747923229</v>
       </c>
       <c r="N5" t="n">
-        <v>12.82458717042465</v>
+        <v>12.78779752603284</v>
       </c>
       <c r="O5" t="n">
-        <v>3.58114327700312</v>
+        <v>3.576003009790798</v>
       </c>
       <c r="P5" t="n">
-        <v>317.782703191071</v>
+        <v>317.783627934631</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -28543,28 +28622,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>0.05942665348373326</v>
+        <v>0.05640874686854118</v>
       </c>
       <c r="J6" t="n">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="K6" t="n">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01101532961172214</v>
+        <v>0.009953175669720427</v>
       </c>
       <c r="M6" t="n">
-        <v>3.199974471985925</v>
+        <v>3.20058643859158</v>
       </c>
       <c r="N6" t="n">
-        <v>16.88326767776108</v>
+        <v>16.91153331382955</v>
       </c>
       <c r="O6" t="n">
-        <v>4.108925367752629</v>
+        <v>4.112363470539727</v>
       </c>
       <c r="P6" t="n">
-        <v>300.1835713180834</v>
+        <v>300.2159529978779</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -28621,28 +28700,28 @@
         <v>0.0881</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1166676407860653</v>
+        <v>0.1162151065115988</v>
       </c>
       <c r="J7" t="n">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="K7" t="n">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="L7" t="n">
-        <v>0.03084097419034393</v>
+        <v>0.03079525395296434</v>
       </c>
       <c r="M7" t="n">
-        <v>3.86955145609384</v>
+        <v>3.860678929137012</v>
       </c>
       <c r="N7" t="n">
-        <v>22.77559245439221</v>
+        <v>22.71187175923722</v>
       </c>
       <c r="O7" t="n">
-        <v>4.772378071191784</v>
+        <v>4.765697405337147</v>
       </c>
       <c r="P7" t="n">
-        <v>291.4992622158975</v>
+        <v>291.5041178399575</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -28699,28 +28778,28 @@
         <v>0.1029</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3464618647631305</v>
+        <v>0.3460648527182931</v>
       </c>
       <c r="J8" t="n">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="K8" t="n">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1625297700815139</v>
+        <v>0.163072839468317</v>
       </c>
       <c r="M8" t="n">
-        <v>4.673188107048607</v>
+        <v>4.661528210897739</v>
       </c>
       <c r="N8" t="n">
-        <v>32.93436000862341</v>
+        <v>32.84104980830201</v>
       </c>
       <c r="O8" t="n">
-        <v>5.738846574759027</v>
+        <v>5.730711108431659</v>
       </c>
       <c r="P8" t="n">
-        <v>291.3900890083148</v>
+        <v>291.3943488872805</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -28777,28 +28856,28 @@
         <v>0.1076</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2763026481791255</v>
+        <v>0.2758754876746776</v>
       </c>
       <c r="J9" t="n">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="K9" t="n">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1053412449597914</v>
+        <v>0.1056412234111931</v>
       </c>
       <c r="M9" t="n">
-        <v>4.801702009529238</v>
+        <v>4.79004668495511</v>
       </c>
       <c r="N9" t="n">
-        <v>34.52478309913319</v>
+        <v>34.42711218863941</v>
       </c>
       <c r="O9" t="n">
-        <v>5.875779360998266</v>
+        <v>5.867462159114399</v>
       </c>
       <c r="P9" t="n">
-        <v>300.1812448721282</v>
+        <v>300.1858282394883</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -28855,28 +28934,28 @@
         <v>0.1135</v>
       </c>
       <c r="I10" t="n">
-        <v>0.130386500394928</v>
+        <v>0.1321102810980468</v>
       </c>
       <c r="J10" t="n">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="K10" t="n">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="L10" t="n">
-        <v>0.02999047472372407</v>
+        <v>0.03092737507668641</v>
       </c>
       <c r="M10" t="n">
-        <v>4.298759325542117</v>
+        <v>4.295799563523085</v>
       </c>
       <c r="N10" t="n">
-        <v>29.27924077079022</v>
+        <v>29.22015485911874</v>
       </c>
       <c r="O10" t="n">
-        <v>5.411029548135015</v>
+        <v>5.40556702475501</v>
       </c>
       <c r="P10" t="n">
-        <v>310.5568941845651</v>
+        <v>310.5383982793295</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -28933,28 +29012,28 @@
         <v>0.2</v>
       </c>
       <c r="I11" t="n">
-        <v>0.2511480214981631</v>
+        <v>0.2520444885494213</v>
       </c>
       <c r="J11" t="n">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="K11" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1101716496872542</v>
+        <v>0.1114701808519453</v>
       </c>
       <c r="M11" t="n">
-        <v>3.892475317067451</v>
+        <v>3.88552381051288</v>
       </c>
       <c r="N11" t="n">
-        <v>27.24697215316252</v>
+        <v>27.17504511086389</v>
       </c>
       <c r="O11" t="n">
-        <v>5.219863231269811</v>
+        <v>5.212968934385077</v>
       </c>
       <c r="P11" t="n">
-        <v>316.0346677751571</v>
+        <v>316.025058362609</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -29011,28 +29090,28 @@
         <v>0.1208</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1968930474521778</v>
+        <v>0.1965721178099113</v>
       </c>
       <c r="J12" t="n">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="K12" t="n">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="L12" t="n">
-        <v>0.05601447607719101</v>
+        <v>0.05617493048791278</v>
       </c>
       <c r="M12" t="n">
-        <v>4.640422103153087</v>
+        <v>4.628801330378072</v>
       </c>
       <c r="N12" t="n">
-        <v>34.78785991323053</v>
+        <v>34.68876308004268</v>
       </c>
       <c r="O12" t="n">
-        <v>5.898123423024525</v>
+        <v>5.889716723242526</v>
       </c>
       <c r="P12" t="n">
-        <v>323.9955437723938</v>
+        <v>323.998987298731</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -29089,28 +29168,28 @@
         <v>0.1693</v>
       </c>
       <c r="I13" t="n">
-        <v>0.182450571727717</v>
+        <v>0.1841729896977896</v>
       </c>
       <c r="J13" t="n">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="K13" t="n">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="L13" t="n">
-        <v>0.0567613920586435</v>
+        <v>0.05807427206669447</v>
       </c>
       <c r="M13" t="n">
-        <v>4.155009167593581</v>
+        <v>4.149717659080765</v>
       </c>
       <c r="N13" t="n">
-        <v>29.45512584353215</v>
+        <v>29.39549492439397</v>
       </c>
       <c r="O13" t="n">
-        <v>5.427257672483604</v>
+        <v>5.421761238231906</v>
       </c>
       <c r="P13" t="n">
-        <v>334.0591282105131</v>
+        <v>334.0406469271962</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -29167,28 +29246,28 @@
         <v>0.2</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1413254355992022</v>
+        <v>0.1421188669130229</v>
       </c>
       <c r="J14" t="n">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="K14" t="n">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="L14" t="n">
-        <v>0.03868675641961894</v>
+        <v>0.03933582189662665</v>
       </c>
       <c r="M14" t="n">
-        <v>3.89001616533135</v>
+        <v>3.881734338726714</v>
       </c>
       <c r="N14" t="n">
-        <v>26.42683580563856</v>
+        <v>26.35620375025436</v>
       </c>
       <c r="O14" t="n">
-        <v>5.140703823956265</v>
+        <v>5.133829345649732</v>
       </c>
       <c r="P14" t="n">
-        <v>350.1223700982431</v>
+        <v>350.1138567007066</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -29245,28 +29324,28 @@
         <v>0.2</v>
       </c>
       <c r="I15" t="n">
-        <v>0.2209338418021049</v>
+        <v>0.2222325136753744</v>
       </c>
       <c r="J15" t="n">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="K15" t="n">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="L15" t="n">
-        <v>0.08296204358221193</v>
+        <v>0.08430655467516279</v>
       </c>
       <c r="M15" t="n">
-        <v>4.027734583623571</v>
+        <v>4.021289225258154</v>
       </c>
       <c r="N15" t="n">
-        <v>28.7299092270843</v>
+        <v>28.66157005745005</v>
       </c>
       <c r="O15" t="n">
-        <v>5.360028845732484</v>
+        <v>5.353650162034316</v>
       </c>
       <c r="P15" t="n">
-        <v>353.5435007920746</v>
+        <v>353.5295662400422</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -29323,28 +29402,28 @@
         <v>0.2</v>
       </c>
       <c r="I16" t="n">
-        <v>0.310020714515874</v>
+        <v>0.3107102068862139</v>
       </c>
       <c r="J16" t="n">
+        <v>348</v>
+      </c>
+      <c r="K16" t="n">
         <v>347</v>
       </c>
-      <c r="K16" t="n">
-        <v>346</v>
-      </c>
       <c r="L16" t="n">
-        <v>0.1673325463472415</v>
+        <v>0.1688144322361801</v>
       </c>
       <c r="M16" t="n">
-        <v>3.933054378798797</v>
+        <v>3.923761235890354</v>
       </c>
       <c r="N16" t="n">
-        <v>25.4511590852525</v>
+        <v>25.3818212057527</v>
       </c>
       <c r="O16" t="n">
-        <v>5.044914180167241</v>
+        <v>5.038037435922117</v>
       </c>
       <c r="P16" t="n">
-        <v>361.1371196722387</v>
+        <v>361.1297107132033</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -29401,28 +29480,28 @@
         <v>0.2</v>
       </c>
       <c r="I17" t="n">
-        <v>0.3846119102244674</v>
+        <v>0.384297241209245</v>
       </c>
       <c r="J17" t="n">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="K17" t="n">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="L17" t="n">
-        <v>0.2786440293959017</v>
+        <v>0.2795776388046914</v>
       </c>
       <c r="M17" t="n">
-        <v>3.479910734541329</v>
+        <v>3.471639798469683</v>
       </c>
       <c r="N17" t="n">
-        <v>20.3914092681424</v>
+        <v>20.33364799993042</v>
       </c>
       <c r="O17" t="n">
-        <v>4.515684806111073</v>
+        <v>4.50928464392418</v>
       </c>
       <c r="P17" t="n">
-        <v>361.8667402146934</v>
+        <v>361.8701165654529</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -29479,28 +29558,28 @@
         <v>0.2</v>
       </c>
       <c r="I18" t="n">
-        <v>0.2951298288110557</v>
+        <v>0.2967200774599868</v>
       </c>
       <c r="J18" t="n">
+        <v>348</v>
+      </c>
+      <c r="K18" t="n">
         <v>347</v>
       </c>
-      <c r="K18" t="n">
-        <v>346</v>
-      </c>
       <c r="L18" t="n">
-        <v>0.1170361365411406</v>
+        <v>0.1187509264612187</v>
       </c>
       <c r="M18" t="n">
-        <v>4.363178839161517</v>
+        <v>4.35806659857709</v>
       </c>
       <c r="N18" t="n">
-        <v>34.62559980716309</v>
+        <v>34.54680627548744</v>
       </c>
       <c r="O18" t="n">
-        <v>5.884352114478117</v>
+        <v>5.87765312650274</v>
       </c>
       <c r="P18" t="n">
-        <v>366.119105058717</v>
+        <v>366.1019209263843</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -29557,28 +29636,28 @@
         <v>0.1952</v>
       </c>
       <c r="I19" t="n">
-        <v>0.3637494568815251</v>
+        <v>0.366180122220172</v>
       </c>
       <c r="J19" t="n">
+        <v>348</v>
+      </c>
+      <c r="K19" t="n">
         <v>347</v>
       </c>
-      <c r="K19" t="n">
-        <v>346</v>
-      </c>
       <c r="L19" t="n">
-        <v>0.1700064964125075</v>
+        <v>0.1725937121421903</v>
       </c>
       <c r="M19" t="n">
-        <v>4.503215636595882</v>
+        <v>4.498886659130778</v>
       </c>
       <c r="N19" t="n">
-        <v>34.03784243020563</v>
+        <v>33.98879346945194</v>
       </c>
       <c r="O19" t="n">
-        <v>5.834195954045907</v>
+        <v>5.829990863582202</v>
       </c>
       <c r="P19" t="n">
-        <v>363.3319427125832</v>
+        <v>363.3056770874786</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -29635,28 +29714,28 @@
         <v>0.2</v>
       </c>
       <c r="I20" t="n">
-        <v>0.3266556454704557</v>
+        <v>0.3288809926834509</v>
       </c>
       <c r="J20" t="n">
+        <v>348</v>
+      </c>
+      <c r="K20" t="n">
         <v>347</v>
       </c>
-      <c r="K20" t="n">
-        <v>346</v>
-      </c>
       <c r="L20" t="n">
-        <v>0.1428490939139171</v>
+        <v>0.1451550053054675</v>
       </c>
       <c r="M20" t="n">
-        <v>4.534650619425588</v>
+        <v>4.53267894551281</v>
       </c>
       <c r="N20" t="n">
-        <v>33.73714096541792</v>
+        <v>33.68102322391701</v>
       </c>
       <c r="O20" t="n">
-        <v>5.808368184388617</v>
+        <v>5.803535407311393</v>
       </c>
       <c r="P20" t="n">
-        <v>352.6528506617302</v>
+        <v>352.6288036920819</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -29694,7 +29773,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U348"/>
+  <dimension ref="A1:U349"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -66909,6 +66988,113 @@
         </is>
       </c>
     </row>
+    <row r="349">
+      <c r="A349" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-09 22:05:44+00:00</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>-36.79217697033975,175.72830992760328</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>-36.792497361466346,175.72748235133366</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>-36.79291733248723,175.72672763948867</t>
+        </is>
+      </c>
+      <c r="E349" t="inlineStr">
+        <is>
+          <t>-36.79359313780946,175.72610582533866</t>
+        </is>
+      </c>
+      <c r="F349" t="inlineStr">
+        <is>
+          <t>-36.794274715285894,175.72549928938537</t>
+        </is>
+      </c>
+      <c r="G349" t="inlineStr">
+        <is>
+          <t>-36.794930901330495,175.7251285640409</t>
+        </is>
+      </c>
+      <c r="H349" t="inlineStr">
+        <is>
+          <t>-36.795620336226065,175.7248476322275</t>
+        </is>
+      </c>
+      <c r="I349" t="inlineStr">
+        <is>
+          <t>-36.79631613314748,175.72459034251546</t>
+        </is>
+      </c>
+      <c r="J349" t="inlineStr">
+        <is>
+          <t>-36.79702103543074,175.724368833261</t>
+        </is>
+      </c>
+      <c r="K349" t="inlineStr">
+        <is>
+          <t>-36.79772914038253,175.72412682536023</t>
+        </is>
+      </c>
+      <c r="L349" t="inlineStr">
+        <is>
+          <t>-36.79843816785285,175.72391094498346</t>
+        </is>
+      </c>
+      <c r="M349" t="inlineStr">
+        <is>
+          <t>-36.79916039360995,175.72379293841792</t>
+        </is>
+      </c>
+      <c r="N349" t="inlineStr">
+        <is>
+          <t>-36.79988706883408,175.72369170095823</t>
+        </is>
+      </c>
+      <c r="O349" t="inlineStr">
+        <is>
+          <t>-36.800611034335276,175.7236674069108</t>
+        </is>
+      </c>
+      <c r="P349" t="inlineStr">
+        <is>
+          <t>-36.801326610681514,175.72367227693908</t>
+        </is>
+      </c>
+      <c r="Q349" t="inlineStr">
+        <is>
+          <t>-36.80203740086299,175.7237165398449</t>
+        </is>
+      </c>
+      <c r="R349" t="inlineStr">
+        <is>
+          <t>-36.80274440457697,175.72381419408194</t>
+        </is>
+      </c>
+      <c r="S349" t="inlineStr">
+        <is>
+          <t>-36.80343451830004,175.72395462346793</t>
+        </is>
+      </c>
+      <c r="T349" t="inlineStr">
+        <is>
+          <t>-36.80415201746852,175.7240523232156</t>
+        </is>
+      </c>
+      <c r="U349" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0175/nzd0175.xlsx
+++ b/data/nzd0175/nzd0175.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U349"/>
+  <dimension ref="A1:U350"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24533,6 +24533,75 @@
         <v>365.1</v>
       </c>
       <c r="U349" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-25 22:06:07+00:00</t>
+        </is>
+      </c>
+      <c r="B350" t="n">
+        <v>315.98</v>
+      </c>
+      <c r="C350" t="n">
+        <v>299.11</v>
+      </c>
+      <c r="D350" t="n">
+        <v>296.14</v>
+      </c>
+      <c r="E350" t="n">
+        <v>316.1</v>
+      </c>
+      <c r="F350" t="n">
+        <v>296.66</v>
+      </c>
+      <c r="G350" t="n">
+        <v>293.33</v>
+      </c>
+      <c r="H350" t="n">
+        <v>299.46</v>
+      </c>
+      <c r="I350" t="n">
+        <v>309.56</v>
+      </c>
+      <c r="J350" t="n">
+        <v>320.18</v>
+      </c>
+      <c r="K350" t="n">
+        <v>324.23</v>
+      </c>
+      <c r="L350" t="n">
+        <v>328.66</v>
+      </c>
+      <c r="M350" t="n">
+        <v>341.85</v>
+      </c>
+      <c r="N350" t="n">
+        <v>354.51</v>
+      </c>
+      <c r="O350" t="n">
+        <v>362</v>
+      </c>
+      <c r="P350" t="n">
+        <v>371.69</v>
+      </c>
+      <c r="Q350" t="n">
+        <v>371.05</v>
+      </c>
+      <c r="R350" t="n">
+        <v>375.13</v>
+      </c>
+      <c r="S350" t="n">
+        <v>377.11</v>
+      </c>
+      <c r="T350" t="n">
+        <v>365.1</v>
+      </c>
+      <c r="U350" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -24549,7 +24618,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B359"/>
+  <dimension ref="A1:B360"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28142,6 +28211,16 @@
       </c>
       <c r="B359" t="n">
         <v>0.52</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>2026-01-25 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B360" t="n">
+        <v>0.49</v>
       </c>
     </row>
   </sheetData>
@@ -28310,28 +28389,28 @@
         <v>0.1008</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3338276441849415</v>
+        <v>0.3354297828129929</v>
       </c>
       <c r="J2" t="n">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="K2" t="n">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1564589310362356</v>
+        <v>0.1584739005729906</v>
       </c>
       <c r="M2" t="n">
-        <v>4.327408551104512</v>
+        <v>4.322188696160956</v>
       </c>
       <c r="N2" t="n">
-        <v>32.10306396555252</v>
+        <v>32.03287797423317</v>
       </c>
       <c r="O2" t="n">
-        <v>5.665956579921215</v>
+        <v>5.659759533251671</v>
       </c>
       <c r="P2" t="n">
-        <v>304.3587881992312</v>
+        <v>304.3415655110389</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -28388,28 +28467,28 @@
         <v>0.1504</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.0773295768358421</v>
+        <v>-0.07717712416160338</v>
       </c>
       <c r="J3" t="n">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="K3" t="n">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="L3" t="n">
-        <v>0.009557960115817554</v>
+        <v>0.009580139864329151</v>
       </c>
       <c r="M3" t="n">
-        <v>4.221657715779804</v>
+        <v>4.21025966252108</v>
       </c>
       <c r="N3" t="n">
-        <v>33.10938661956995</v>
+        <v>33.01471470628704</v>
       </c>
       <c r="O3" t="n">
-        <v>5.754075652923756</v>
+        <v>5.745843254587358</v>
       </c>
       <c r="P3" t="n">
-        <v>300.9017263822326</v>
+        <v>300.9000875447272</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -28466,28 +28545,28 @@
         <v>0.1503</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.05570618281974439</v>
+        <v>-0.05888142907364837</v>
       </c>
       <c r="J4" t="n">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="K4" t="n">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="L4" t="n">
-        <v>0.005783174518133705</v>
+        <v>0.006477974579238155</v>
       </c>
       <c r="M4" t="n">
-        <v>3.965316278058648</v>
+        <v>3.970786542010063</v>
       </c>
       <c r="N4" t="n">
-        <v>28.5047756068518</v>
+        <v>28.50872658321924</v>
       </c>
       <c r="O4" t="n">
-        <v>5.338986383842143</v>
+        <v>5.339356382862942</v>
       </c>
       <c r="P4" t="n">
-        <v>303.1117642236467</v>
+        <v>303.1458975222311</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -28544,28 +28623,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.04965998781471327</v>
+        <v>-0.04987020306647569</v>
       </c>
       <c r="J5" t="n">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="K5" t="n">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01019908782579149</v>
+        <v>0.01034868112824072</v>
       </c>
       <c r="M5" t="n">
-        <v>2.698833747923229</v>
+        <v>2.692046822576956</v>
       </c>
       <c r="N5" t="n">
-        <v>12.78779752603284</v>
+        <v>12.75153157540761</v>
       </c>
       <c r="O5" t="n">
-        <v>3.576003009790798</v>
+        <v>3.57092867128533</v>
       </c>
       <c r="P5" t="n">
-        <v>317.783627934631</v>
+        <v>317.7858877089545</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -28622,28 +28701,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>0.05640874686854118</v>
+        <v>0.05348763920721139</v>
       </c>
       <c r="J6" t="n">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="K6" t="n">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="L6" t="n">
-        <v>0.009953175669720427</v>
+        <v>0.008975834000883642</v>
       </c>
       <c r="M6" t="n">
-        <v>3.20058643859158</v>
+        <v>3.200824420773774</v>
       </c>
       <c r="N6" t="n">
-        <v>16.91153331382955</v>
+        <v>16.93554461202254</v>
       </c>
       <c r="O6" t="n">
-        <v>4.112363470539727</v>
+        <v>4.115281838710751</v>
       </c>
       <c r="P6" t="n">
-        <v>300.2159529978779</v>
+        <v>300.2473543545061</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -28700,28 +28779,28 @@
         <v>0.0881</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1162151065115988</v>
+        <v>0.1154910061531696</v>
       </c>
       <c r="J7" t="n">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="K7" t="n">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="L7" t="n">
-        <v>0.03079525395296434</v>
+        <v>0.0306046902758752</v>
       </c>
       <c r="M7" t="n">
-        <v>3.860678929137012</v>
+        <v>3.853186574857735</v>
       </c>
       <c r="N7" t="n">
-        <v>22.71187175923722</v>
+        <v>22.65124774697331</v>
       </c>
       <c r="O7" t="n">
-        <v>4.765697405337147</v>
+        <v>4.75933269975669</v>
       </c>
       <c r="P7" t="n">
-        <v>291.5041178399575</v>
+        <v>291.5119017822924</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -28778,28 +28857,28 @@
         <v>0.1029</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3460648527182931</v>
+        <v>0.3454188832123399</v>
       </c>
       <c r="J8" t="n">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="K8" t="n">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="L8" t="n">
-        <v>0.163072839468317</v>
+        <v>0.1634072363152674</v>
       </c>
       <c r="M8" t="n">
-        <v>4.661528210897739</v>
+        <v>4.65102724077465</v>
       </c>
       <c r="N8" t="n">
-        <v>32.84104980830201</v>
+        <v>32.75049324806405</v>
       </c>
       <c r="O8" t="n">
-        <v>5.730711108431659</v>
+        <v>5.722804666250985</v>
       </c>
       <c r="P8" t="n">
-        <v>291.3943488872805</v>
+        <v>291.4012929376817</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -28856,28 +28935,28 @@
         <v>0.1076</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2758754876746776</v>
+        <v>0.2770646911409552</v>
       </c>
       <c r="J9" t="n">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="K9" t="n">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1056412234111931</v>
+        <v>0.1070234533923476</v>
       </c>
       <c r="M9" t="n">
-        <v>4.79004668495511</v>
+        <v>4.782090200930909</v>
       </c>
       <c r="N9" t="n">
-        <v>34.42711218863941</v>
+        <v>34.34047780279686</v>
       </c>
       <c r="O9" t="n">
-        <v>5.867462159114399</v>
+        <v>5.860074897370925</v>
       </c>
       <c r="P9" t="n">
-        <v>300.1858282394883</v>
+        <v>300.1730445264324</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -28934,28 +29013,28 @@
         <v>0.1135</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1321102810980468</v>
+        <v>0.1356596294743152</v>
       </c>
       <c r="J10" t="n">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="K10" t="n">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="L10" t="n">
-        <v>0.03092737507668641</v>
+        <v>0.0326395580532074</v>
       </c>
       <c r="M10" t="n">
-        <v>4.295799563523085</v>
+        <v>4.302825934040832</v>
       </c>
       <c r="N10" t="n">
-        <v>29.22015485911874</v>
+        <v>29.24342138314667</v>
       </c>
       <c r="O10" t="n">
-        <v>5.40556702475501</v>
+        <v>5.407718685651711</v>
       </c>
       <c r="P10" t="n">
-        <v>310.5383982793295</v>
+        <v>310.5002434534609</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -29012,28 +29091,28 @@
         <v>0.2</v>
       </c>
       <c r="I11" t="n">
-        <v>0.2520444885494213</v>
+        <v>0.2529218402896784</v>
       </c>
       <c r="J11" t="n">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="K11" t="n">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1114701808519453</v>
+        <v>0.1127627454071787</v>
       </c>
       <c r="M11" t="n">
-        <v>3.88552381051288</v>
+        <v>3.878506424763026</v>
       </c>
       <c r="N11" t="n">
-        <v>27.17504511086389</v>
+        <v>27.10331280640282</v>
       </c>
       <c r="O11" t="n">
-        <v>5.212968934385077</v>
+        <v>5.206084210460182</v>
       </c>
       <c r="P11" t="n">
-        <v>316.025058362609</v>
+        <v>316.0156361919842</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -29090,28 +29169,28 @@
         <v>0.1208</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1965721178099113</v>
+        <v>0.1962507700302056</v>
       </c>
       <c r="J12" t="n">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="K12" t="n">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="L12" t="n">
-        <v>0.05617493048791278</v>
+        <v>0.05633396202152841</v>
       </c>
       <c r="M12" t="n">
-        <v>4.628801330378072</v>
+        <v>4.617241989377582</v>
       </c>
       <c r="N12" t="n">
-        <v>34.68876308004268</v>
+        <v>34.59024535279598</v>
       </c>
       <c r="O12" t="n">
-        <v>5.889716723242526</v>
+        <v>5.881347239603863</v>
       </c>
       <c r="P12" t="n">
-        <v>323.998987298731</v>
+        <v>324.0024417267776</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -29168,28 +29247,28 @@
         <v>0.1693</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1841729896977896</v>
+        <v>0.1858662661557319</v>
       </c>
       <c r="J13" t="n">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="K13" t="n">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="L13" t="n">
-        <v>0.05807427206669447</v>
+        <v>0.05938807736487184</v>
       </c>
       <c r="M13" t="n">
-        <v>4.149717659080765</v>
+        <v>4.144317196373525</v>
       </c>
       <c r="N13" t="n">
-        <v>29.39549492439397</v>
+        <v>29.33561772849335</v>
       </c>
       <c r="O13" t="n">
-        <v>5.421761238231906</v>
+        <v>5.416236491189556</v>
       </c>
       <c r="P13" t="n">
-        <v>334.0406469271962</v>
+        <v>334.0224445245153</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -29246,28 +29325,28 @@
         <v>0.2</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1421188669130229</v>
+        <v>0.1424818490860869</v>
       </c>
       <c r="J14" t="n">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="K14" t="n">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="L14" t="n">
-        <v>0.03933582189662665</v>
+        <v>0.03976705220304888</v>
       </c>
       <c r="M14" t="n">
-        <v>3.881734338726714</v>
+        <v>3.871927120781942</v>
       </c>
       <c r="N14" t="n">
-        <v>26.35620375025436</v>
+        <v>26.28180352668539</v>
       </c>
       <c r="O14" t="n">
-        <v>5.133829345649732</v>
+        <v>5.126578149866184</v>
       </c>
       <c r="P14" t="n">
-        <v>350.1138567007066</v>
+        <v>350.109954710781</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -29324,28 +29403,28 @@
         <v>0.2</v>
       </c>
       <c r="I15" t="n">
-        <v>0.2222325136753744</v>
+        <v>0.223720412748526</v>
       </c>
       <c r="J15" t="n">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="K15" t="n">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="L15" t="n">
-        <v>0.08430655467516279</v>
+        <v>0.08578349613572667</v>
       </c>
       <c r="M15" t="n">
-        <v>4.021289225258154</v>
+        <v>4.015602619812791</v>
       </c>
       <c r="N15" t="n">
-        <v>28.66157005745005</v>
+        <v>28.5982470644585</v>
       </c>
       <c r="O15" t="n">
-        <v>5.353650162034316</v>
+        <v>5.347732890156211</v>
       </c>
       <c r="P15" t="n">
-        <v>353.5295662400422</v>
+        <v>353.5135716055268</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -29402,28 +29481,28 @@
         <v>0.2</v>
       </c>
       <c r="I16" t="n">
-        <v>0.3107102068862139</v>
+        <v>0.3120542563782684</v>
       </c>
       <c r="J16" t="n">
+        <v>349</v>
+      </c>
+      <c r="K16" t="n">
         <v>348</v>
       </c>
-      <c r="K16" t="n">
-        <v>347</v>
-      </c>
       <c r="L16" t="n">
-        <v>0.1688144322361801</v>
+        <v>0.1708325686788512</v>
       </c>
       <c r="M16" t="n">
-        <v>3.923761235890354</v>
+        <v>3.916490635995872</v>
       </c>
       <c r="N16" t="n">
-        <v>25.3818212057527</v>
+        <v>25.32422924101607</v>
       </c>
       <c r="O16" t="n">
-        <v>5.038037435922117</v>
+        <v>5.032318475714358</v>
       </c>
       <c r="P16" t="n">
-        <v>361.1297107132033</v>
+        <v>361.1152412626506</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -29480,28 +29559,28 @@
         <v>0.2</v>
       </c>
       <c r="I17" t="n">
-        <v>0.384297241209245</v>
+        <v>0.3837098973398054</v>
       </c>
       <c r="J17" t="n">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="K17" t="n">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="L17" t="n">
-        <v>0.2795776388046914</v>
+        <v>0.2802003343080829</v>
       </c>
       <c r="M17" t="n">
-        <v>3.471639798469683</v>
+        <v>3.464897088775996</v>
       </c>
       <c r="N17" t="n">
-        <v>20.33364799993042</v>
+        <v>20.27831520180594</v>
       </c>
       <c r="O17" t="n">
-        <v>4.50928464392418</v>
+        <v>4.503145034507098</v>
       </c>
       <c r="P17" t="n">
-        <v>361.8701165654529</v>
+        <v>361.8764304013146</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -29558,28 +29637,28 @@
         <v>0.2</v>
       </c>
       <c r="I18" t="n">
-        <v>0.2967200774599868</v>
+        <v>0.2973941787489796</v>
       </c>
       <c r="J18" t="n">
+        <v>349</v>
+      </c>
+      <c r="K18" t="n">
         <v>348</v>
       </c>
-      <c r="K18" t="n">
-        <v>347</v>
-      </c>
       <c r="L18" t="n">
-        <v>0.1187509264612187</v>
+        <v>0.1198808028639208</v>
       </c>
       <c r="M18" t="n">
-        <v>4.35806659857709</v>
+        <v>4.348685075060343</v>
       </c>
       <c r="N18" t="n">
-        <v>34.54680627548744</v>
+        <v>34.45133402427684</v>
       </c>
       <c r="O18" t="n">
-        <v>5.87765312650274</v>
+        <v>5.86952587729851</v>
       </c>
       <c r="P18" t="n">
-        <v>366.1019209263843</v>
+        <v>366.0946231989115</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -29636,28 +29715,28 @@
         <v>0.1952</v>
       </c>
       <c r="I19" t="n">
-        <v>0.366180122220172</v>
+        <v>0.368566736525503</v>
       </c>
       <c r="J19" t="n">
+        <v>349</v>
+      </c>
+      <c r="K19" t="n">
         <v>348</v>
       </c>
-      <c r="K19" t="n">
-        <v>347</v>
-      </c>
       <c r="L19" t="n">
-        <v>0.1725937121421903</v>
+        <v>0.1751667744839039</v>
       </c>
       <c r="M19" t="n">
-        <v>4.498886659130778</v>
+        <v>4.494402064823273</v>
       </c>
       <c r="N19" t="n">
-        <v>33.98879346945194</v>
+        <v>33.93875867074028</v>
       </c>
       <c r="O19" t="n">
-        <v>5.829990863582202</v>
+        <v>5.825698127326911</v>
       </c>
       <c r="P19" t="n">
-        <v>363.3056770874786</v>
+        <v>363.2798399305599</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -29714,28 +29793,28 @@
         <v>0.2</v>
       </c>
       <c r="I20" t="n">
-        <v>0.3288809926834509</v>
+        <v>0.3310661726163359</v>
       </c>
       <c r="J20" t="n">
+        <v>349</v>
+      </c>
+      <c r="K20" t="n">
         <v>348</v>
       </c>
-      <c r="K20" t="n">
-        <v>347</v>
-      </c>
       <c r="L20" t="n">
-        <v>0.1451550053054675</v>
+        <v>0.1474506870256138</v>
       </c>
       <c r="M20" t="n">
-        <v>4.53267894551281</v>
+        <v>4.530612332826387</v>
       </c>
       <c r="N20" t="n">
-        <v>33.68102322391701</v>
+        <v>33.62417134269225</v>
       </c>
       <c r="O20" t="n">
-        <v>5.803535407311393</v>
+        <v>5.798635300024674</v>
       </c>
       <c r="P20" t="n">
-        <v>352.6288036920819</v>
+        <v>352.6051472358645</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -29773,7 +29852,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U349"/>
+  <dimension ref="A1:U350"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -67095,6 +67174,113 @@
         </is>
       </c>
     </row>
+    <row r="350">
+      <c r="A350" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-25 22:06:07+00:00</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>-36.792183624683304,175.72831643847906</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>-36.79249806937882,175.72748304397797</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>-36.79292031119707,175.72673071827714</t>
+        </is>
+      </c>
+      <c r="E350" t="inlineStr">
+        <is>
+          <t>-36.79359200394604,175.7261038043665</t>
+        </is>
+      </c>
+      <c r="F350" t="inlineStr">
+        <is>
+          <t>-36.79427504229766,175.72550033304603</t>
+        </is>
+      </c>
+      <c r="G350" t="inlineStr">
+        <is>
+          <t>-36.79492933166447,175.72512355443055</t>
+        </is>
+      </c>
+      <c r="H350" t="inlineStr">
+        <is>
+          <t>-36.79561899378292,175.72484323394872</t>
+        </is>
+      </c>
+      <c r="I350" t="inlineStr">
+        <is>
+          <t>-36.79632487493142,175.72461976142466</t>
+        </is>
+      </c>
+      <c r="J350" t="inlineStr">
+        <is>
+          <t>-36.79703079278261,175.7244025609321</t>
+        </is>
+      </c>
+      <c r="K350" t="inlineStr">
+        <is>
+          <t>-36.79772914038253,175.72412682536023</t>
+        </is>
+      </c>
+      <c r="L350" t="inlineStr">
+        <is>
+          <t>-36.79843816785285,175.72391094498346</t>
+        </is>
+      </c>
+      <c r="M350" t="inlineStr">
+        <is>
+          <t>-36.79916039360995,175.72379293841792</t>
+        </is>
+      </c>
+      <c r="N350" t="inlineStr">
+        <is>
+          <t>-36.79988596528335,175.72368375346494</t>
+        </is>
+      </c>
+      <c r="O350" t="inlineStr">
+        <is>
+          <t>-36.80061132113862,175.72367153613845</t>
+        </is>
+      </c>
+      <c r="P350" t="inlineStr">
+        <is>
+          <t>-36.8013267645932,175.72368526953267</t>
+        </is>
+      </c>
+      <c r="Q350" t="inlineStr">
+        <is>
+          <t>-36.80203765288661,175.72371139654217</t>
+        </is>
+      </c>
+      <c r="R350" t="inlineStr">
+        <is>
+          <t>-36.8027460439346,175.72379728962179</t>
+        </is>
+      </c>
+      <c r="S350" t="inlineStr">
+        <is>
+          <t>-36.80343451830004,175.72395462346793</t>
+        </is>
+      </c>
+      <c r="T350" t="inlineStr">
+        <is>
+          <t>-36.80415201746852,175.7240523232156</t>
+        </is>
+      </c>
+      <c r="U350" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0175/nzd0175.xlsx
+++ b/data/nzd0175/nzd0175.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U350"/>
+  <dimension ref="A1:U351"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24602,6 +24602,75 @@
         <v>365.1</v>
       </c>
       <c r="U350" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-26 22:06:01+00:00</t>
+        </is>
+      </c>
+      <c r="B351" t="n">
+        <v>319.15</v>
+      </c>
+      <c r="C351" t="n">
+        <v>303.97</v>
+      </c>
+      <c r="D351" t="n">
+        <v>297.26</v>
+      </c>
+      <c r="E351" t="n">
+        <v>318.69</v>
+      </c>
+      <c r="F351" t="n">
+        <v>297.65</v>
+      </c>
+      <c r="G351" t="n">
+        <v>295.24</v>
+      </c>
+      <c r="H351" t="n">
+        <v>300.93</v>
+      </c>
+      <c r="I351" t="n">
+        <v>312.64</v>
+      </c>
+      <c r="J351" t="n">
+        <v>323.12</v>
+      </c>
+      <c r="K351" t="n">
+        <v>327.15</v>
+      </c>
+      <c r="L351" t="n">
+        <v>331.38</v>
+      </c>
+      <c r="M351" t="n">
+        <v>346.18</v>
+      </c>
+      <c r="N351" t="n">
+        <v>355.53</v>
+      </c>
+      <c r="O351" t="n">
+        <v>363.08</v>
+      </c>
+      <c r="P351" t="n">
+        <v>373.86</v>
+      </c>
+      <c r="Q351" t="n">
+        <v>371.82</v>
+      </c>
+      <c r="R351" t="n">
+        <v>376.66</v>
+      </c>
+      <c r="S351" t="n">
+        <v>378.8</v>
+      </c>
+      <c r="T351" t="n">
+        <v>366.21</v>
+      </c>
+      <c r="U351" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -24618,7 +24687,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B360"/>
+  <dimension ref="A1:B361"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28221,6 +28290,16 @@
       </c>
       <c r="B360" t="n">
         <v>0.49</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>2026-02-26 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B361" t="n">
+        <v>-0.42</v>
       </c>
     </row>
   </sheetData>
@@ -28389,28 +28468,28 @@
         <v>0.1008</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3354297828129929</v>
+        <v>0.3388257590108897</v>
       </c>
       <c r="J2" t="n">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="K2" t="n">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1584739005729906</v>
+        <v>0.1616203100694189</v>
       </c>
       <c r="M2" t="n">
-        <v>4.322188696160956</v>
+        <v>4.325106286647726</v>
       </c>
       <c r="N2" t="n">
-        <v>32.03287797423317</v>
+        <v>32.03923701415271</v>
       </c>
       <c r="O2" t="n">
-        <v>5.659759533251671</v>
+        <v>5.660321281884334</v>
       </c>
       <c r="P2" t="n">
-        <v>304.3415655110389</v>
+        <v>304.3049242166744</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -28467,28 +28546,28 @@
         <v>0.1504</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.07717712416160338</v>
+        <v>-0.07421677047954847</v>
       </c>
       <c r="J3" t="n">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="K3" t="n">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="L3" t="n">
-        <v>0.009580139864329151</v>
+        <v>0.008901442478785215</v>
       </c>
       <c r="M3" t="n">
-        <v>4.21025966252108</v>
+        <v>4.211654018423794</v>
       </c>
       <c r="N3" t="n">
-        <v>33.01471470628704</v>
+        <v>32.99476739233273</v>
       </c>
       <c r="O3" t="n">
-        <v>5.745843254587358</v>
+        <v>5.744107188443886</v>
       </c>
       <c r="P3" t="n">
-        <v>300.9000875447272</v>
+        <v>300.868146451985</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -28545,28 +28624,28 @@
         <v>0.1503</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.05888142907364837</v>
+        <v>-0.06137389741603903</v>
       </c>
       <c r="J4" t="n">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="K4" t="n">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="L4" t="n">
-        <v>0.006477974579238155</v>
+        <v>0.007065332588072848</v>
       </c>
       <c r="M4" t="n">
-        <v>3.970786542010063</v>
+        <v>3.972503604885362</v>
       </c>
       <c r="N4" t="n">
-        <v>28.50872658321924</v>
+        <v>28.47999981104435</v>
       </c>
       <c r="O4" t="n">
-        <v>5.339356382862942</v>
+        <v>5.336665607947002</v>
       </c>
       <c r="P4" t="n">
-        <v>303.1458975222311</v>
+        <v>303.1727903097259</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -28623,28 +28702,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.04987020306647569</v>
+        <v>-0.04858386109806333</v>
       </c>
       <c r="J5" t="n">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="K5" t="n">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01034868112824072</v>
+        <v>0.009877754714854636</v>
       </c>
       <c r="M5" t="n">
-        <v>2.692046822576956</v>
+        <v>2.691278819255225</v>
       </c>
       <c r="N5" t="n">
-        <v>12.75153157540761</v>
+        <v>12.7291424215223</v>
       </c>
       <c r="O5" t="n">
-        <v>3.57092867128533</v>
+        <v>3.567792373656615</v>
       </c>
       <c r="P5" t="n">
-        <v>317.7858877089545</v>
+        <v>317.7720085672964</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -28701,28 +28780,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>0.05348763920721139</v>
+        <v>0.05116642545954282</v>
       </c>
       <c r="J6" t="n">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="K6" t="n">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="L6" t="n">
-        <v>0.008975834000883642</v>
+        <v>0.008249470770334777</v>
       </c>
       <c r="M6" t="n">
-        <v>3.200824420773774</v>
+        <v>3.199053201285746</v>
       </c>
       <c r="N6" t="n">
-        <v>16.93554461202254</v>
+        <v>16.93288740724056</v>
       </c>
       <c r="O6" t="n">
-        <v>4.115281838710751</v>
+        <v>4.114958980019189</v>
       </c>
       <c r="P6" t="n">
-        <v>300.2473543545061</v>
+        <v>300.272399369917</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -28779,28 +28858,28 @@
         <v>0.0881</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1154910061531696</v>
+        <v>0.115870258822912</v>
       </c>
       <c r="J7" t="n">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="K7" t="n">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0306046902758752</v>
+        <v>0.03098738392032963</v>
       </c>
       <c r="M7" t="n">
-        <v>3.853186574857735</v>
+        <v>3.844046976500309</v>
       </c>
       <c r="N7" t="n">
-        <v>22.65124774697331</v>
+        <v>22.58775065221572</v>
       </c>
       <c r="O7" t="n">
-        <v>4.75933269975669</v>
+        <v>4.752657220147032</v>
       </c>
       <c r="P7" t="n">
-        <v>291.5119017822924</v>
+        <v>291.5078097899165</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -28857,28 +28936,28 @@
         <v>0.1029</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3454188832123399</v>
+        <v>0.3456131991951738</v>
       </c>
       <c r="J8" t="n">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="K8" t="n">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1634072363152674</v>
+        <v>0.1644260281299088</v>
       </c>
       <c r="M8" t="n">
-        <v>4.65102724077465</v>
+        <v>4.638795289452094</v>
       </c>
       <c r="N8" t="n">
-        <v>32.75049324806405</v>
+        <v>32.65724088111448</v>
       </c>
       <c r="O8" t="n">
-        <v>5.722804666250985</v>
+        <v>5.714651422537903</v>
       </c>
       <c r="P8" t="n">
-        <v>291.4012929376817</v>
+        <v>291.399196341972</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -28935,28 +29014,28 @@
         <v>0.1076</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2770646911409552</v>
+        <v>0.2800055960503909</v>
       </c>
       <c r="J9" t="n">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="K9" t="n">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1070234533923476</v>
+        <v>0.1094649812899168</v>
       </c>
       <c r="M9" t="n">
-        <v>4.782090200930909</v>
+        <v>4.782862056725702</v>
       </c>
       <c r="N9" t="n">
-        <v>34.34047780279686</v>
+        <v>34.31576848338717</v>
       </c>
       <c r="O9" t="n">
-        <v>5.860074897370925</v>
+        <v>5.857966241229731</v>
       </c>
       <c r="P9" t="n">
-        <v>300.1730445264324</v>
+        <v>300.1413132785657</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -29013,28 +29092,28 @@
         <v>0.1135</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1356596294743152</v>
+        <v>0.1408611619258088</v>
       </c>
       <c r="J10" t="n">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="K10" t="n">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0326395580532074</v>
+        <v>0.03504934668449411</v>
       </c>
       <c r="M10" t="n">
-        <v>4.302825934040832</v>
+        <v>4.318977447496922</v>
       </c>
       <c r="N10" t="n">
-        <v>29.24342138314667</v>
+        <v>29.38950168754306</v>
       </c>
       <c r="O10" t="n">
-        <v>5.407718685651711</v>
+        <v>5.421208508030571</v>
       </c>
       <c r="P10" t="n">
-        <v>310.5002434534609</v>
+        <v>310.4441208923488</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -29091,28 +29170,28 @@
         <v>0.2</v>
       </c>
       <c r="I11" t="n">
-        <v>0.2529218402896784</v>
+        <v>0.2554649910439036</v>
       </c>
       <c r="J11" t="n">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="K11" t="n">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1127627454071787</v>
+        <v>0.1152138602825584</v>
       </c>
       <c r="M11" t="n">
-        <v>3.878506424763026</v>
+        <v>3.879359274724271</v>
       </c>
       <c r="N11" t="n">
-        <v>27.10331280640282</v>
+        <v>27.08069464258389</v>
       </c>
       <c r="O11" t="n">
-        <v>5.206084210460182</v>
+        <v>5.203911475283173</v>
       </c>
       <c r="P11" t="n">
-        <v>316.0156361919842</v>
+        <v>315.9882223832134</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -29169,28 +29248,28 @@
         <v>0.1208</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1962507700302056</v>
+        <v>0.1974930434199366</v>
       </c>
       <c r="J12" t="n">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="K12" t="n">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="L12" t="n">
-        <v>0.05633396202152841</v>
+        <v>0.05732874883036443</v>
       </c>
       <c r="M12" t="n">
-        <v>4.617241989377582</v>
+        <v>4.609718114678083</v>
       </c>
       <c r="N12" t="n">
-        <v>34.59024535279598</v>
+        <v>34.50451410854335</v>
       </c>
       <c r="O12" t="n">
-        <v>5.881347239603863</v>
+        <v>5.874054316104282</v>
       </c>
       <c r="P12" t="n">
-        <v>324.0024417267776</v>
+        <v>323.9890380683589</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -29247,28 +29326,28 @@
         <v>0.1693</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1858662661557319</v>
+        <v>0.1900334351053822</v>
       </c>
       <c r="J13" t="n">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="K13" t="n">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="L13" t="n">
-        <v>0.05938807736487184</v>
+        <v>0.06198933908136051</v>
       </c>
       <c r="M13" t="n">
-        <v>4.144317196373525</v>
+        <v>4.148663288160326</v>
       </c>
       <c r="N13" t="n">
-        <v>29.33561772849335</v>
+        <v>29.39918684302813</v>
       </c>
       <c r="O13" t="n">
-        <v>5.416236491189556</v>
+        <v>5.422101699804987</v>
       </c>
       <c r="P13" t="n">
-        <v>334.0224445245153</v>
+        <v>333.9774823530355</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -29325,28 +29404,28 @@
         <v>0.2</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1424818490860869</v>
+        <v>0.143421323074616</v>
       </c>
       <c r="J14" t="n">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="K14" t="n">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="L14" t="n">
-        <v>0.03976705220304888</v>
+        <v>0.04050583863551216</v>
       </c>
       <c r="M14" t="n">
-        <v>3.871927120781942</v>
+        <v>3.864227848813145</v>
       </c>
       <c r="N14" t="n">
-        <v>26.28180352668539</v>
+        <v>26.21420368152641</v>
       </c>
       <c r="O14" t="n">
-        <v>5.126578149866184</v>
+        <v>5.11998082823817</v>
       </c>
       <c r="P14" t="n">
-        <v>350.109954710781</v>
+        <v>350.0998181429856</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -29403,28 +29482,28 @@
         <v>0.2</v>
       </c>
       <c r="I15" t="n">
-        <v>0.223720412748526</v>
+        <v>0.2258079349644337</v>
       </c>
       <c r="J15" t="n">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="K15" t="n">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="L15" t="n">
-        <v>0.08578349613572667</v>
+        <v>0.08765234936244271</v>
       </c>
       <c r="M15" t="n">
-        <v>4.015602619812791</v>
+        <v>4.012417354171984</v>
       </c>
       <c r="N15" t="n">
-        <v>28.5982470644585</v>
+        <v>28.55352348075139</v>
       </c>
       <c r="O15" t="n">
-        <v>5.347732890156211</v>
+        <v>5.343549707895622</v>
       </c>
       <c r="P15" t="n">
-        <v>353.5135716055268</v>
+        <v>353.4910480330551</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -29481,28 +29560,28 @@
         <v>0.2</v>
       </c>
       <c r="I16" t="n">
-        <v>0.3120542563782684</v>
+        <v>0.3146223192715319</v>
       </c>
       <c r="J16" t="n">
+        <v>350</v>
+      </c>
+      <c r="K16" t="n">
         <v>349</v>
       </c>
-      <c r="K16" t="n">
-        <v>348</v>
-      </c>
       <c r="L16" t="n">
-        <v>0.1708325686788512</v>
+        <v>0.1737547565751607</v>
       </c>
       <c r="M16" t="n">
-        <v>3.916490635995872</v>
+        <v>3.912908132075207</v>
       </c>
       <c r="N16" t="n">
-        <v>25.32422924101607</v>
+        <v>25.30764663571492</v>
       </c>
       <c r="O16" t="n">
-        <v>5.032318475714358</v>
+        <v>5.030670595031534</v>
       </c>
       <c r="P16" t="n">
-        <v>361.1152412626506</v>
+        <v>361.0874920126865</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -29559,28 +29638,28 @@
         <v>0.2</v>
       </c>
       <c r="I17" t="n">
-        <v>0.3837098973398054</v>
+        <v>0.3835572228814936</v>
       </c>
       <c r="J17" t="n">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="K17" t="n">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="L17" t="n">
-        <v>0.2802003343080829</v>
+        <v>0.2813136187619889</v>
       </c>
       <c r="M17" t="n">
-        <v>3.464897088775996</v>
+        <v>3.455821326472964</v>
       </c>
       <c r="N17" t="n">
-        <v>20.27831520180594</v>
+        <v>20.22057499392064</v>
       </c>
       <c r="O17" t="n">
-        <v>4.503145034507098</v>
+        <v>4.496729366319553</v>
       </c>
       <c r="P17" t="n">
-        <v>361.8764304013146</v>
+        <v>361.878077700778</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -29637,28 +29716,28 @@
         <v>0.2</v>
       </c>
       <c r="I18" t="n">
-        <v>0.2973941787489796</v>
+        <v>0.2989374287870309</v>
       </c>
       <c r="J18" t="n">
+        <v>350</v>
+      </c>
+      <c r="K18" t="n">
         <v>349</v>
       </c>
-      <c r="K18" t="n">
-        <v>348</v>
-      </c>
       <c r="L18" t="n">
-        <v>0.1198808028639208</v>
+        <v>0.1215923729829992</v>
       </c>
       <c r="M18" t="n">
-        <v>4.348685075060343</v>
+        <v>4.343340524333981</v>
       </c>
       <c r="N18" t="n">
-        <v>34.45133402427684</v>
+        <v>34.37252386565712</v>
       </c>
       <c r="O18" t="n">
-        <v>5.86952587729851</v>
+        <v>5.862808530530152</v>
       </c>
       <c r="P18" t="n">
-        <v>366.0946231989115</v>
+        <v>366.0778548814452</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -29715,28 +29794,28 @@
         <v>0.1952</v>
       </c>
       <c r="I19" t="n">
-        <v>0.368566736525503</v>
+        <v>0.3718981818567377</v>
       </c>
       <c r="J19" t="n">
+        <v>350</v>
+      </c>
+      <c r="K19" t="n">
         <v>349</v>
       </c>
-      <c r="K19" t="n">
-        <v>348</v>
-      </c>
       <c r="L19" t="n">
-        <v>0.1751667744839039</v>
+        <v>0.1783110092966608</v>
       </c>
       <c r="M19" t="n">
-        <v>4.494402064823273</v>
+        <v>4.493508826794704</v>
       </c>
       <c r="N19" t="n">
-        <v>33.93875867074028</v>
+        <v>33.93426828899536</v>
       </c>
       <c r="O19" t="n">
-        <v>5.825698127326911</v>
+        <v>5.825312720274797</v>
       </c>
       <c r="P19" t="n">
-        <v>363.2798399305599</v>
+        <v>363.2436418216609</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -29793,28 +29872,28 @@
         <v>0.2</v>
       </c>
       <c r="I20" t="n">
-        <v>0.3310661726163359</v>
+        <v>0.3338629533318511</v>
       </c>
       <c r="J20" t="n">
+        <v>350</v>
+      </c>
+      <c r="K20" t="n">
         <v>349</v>
       </c>
-      <c r="K20" t="n">
-        <v>348</v>
-      </c>
       <c r="L20" t="n">
-        <v>0.1474506870256138</v>
+        <v>0.1501391620031768</v>
       </c>
       <c r="M20" t="n">
-        <v>4.530612332826387</v>
+        <v>4.531509527782696</v>
       </c>
       <c r="N20" t="n">
-        <v>33.62417134269225</v>
+        <v>33.59319880515292</v>
       </c>
       <c r="O20" t="n">
-        <v>5.798635300024674</v>
+        <v>5.79596400999462</v>
       </c>
       <c r="P20" t="n">
-        <v>352.6051472358645</v>
+        <v>352.5747585718341</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -29852,7 +29931,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U350"/>
+  <dimension ref="A1:U351"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -67281,6 +67360,113 @@
         </is>
       </c>
     </row>
+    <row r="351">
+      <c r="A351" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-26 22:06:01+00:00</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>-36.79220606539208,175.72833839537708</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>-36.79253247391993,175.7275167065063</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>-36.792928069696686,175.7267387374482</t>
+        </is>
+      </c>
+      <c r="E351" t="inlineStr">
+        <is>
+          <t>-36.79360535260846,175.72612759672407</t>
+        </is>
+      </c>
+      <c r="F351" t="inlineStr">
+        <is>
+          <t>-36.79427827971356,175.7255106652871</t>
+        </is>
+      </c>
+      <c r="G351" t="inlineStr">
+        <is>
+          <t>-36.794935577625914,175.72514348850623</t>
+        </is>
+      </c>
+      <c r="H351" t="inlineStr">
+        <is>
+          <t>-36.795623692333194,175.72485862792507</t>
+        </is>
+      </c>
+      <c r="I351" t="inlineStr">
+        <is>
+          <t>-36.79633449088501,175.72465212223207</t>
+        </is>
+      </c>
+      <c r="J351" t="inlineStr">
+        <is>
+          <t>-36.79703975734088,175.72443354823702</t>
+        </is>
+      </c>
+      <c r="K351" t="inlineStr">
+        <is>
+          <t>-36.79773705049305,175.72415801891188</t>
+        </is>
+      </c>
+      <c r="L351" t="inlineStr">
+        <is>
+          <t>-36.79844480262145,175.723940274285</t>
+        </is>
+      </c>
+      <c r="M351" t="inlineStr">
+        <is>
+          <t>-36.799170612499296,175.72383974642344</t>
+        </is>
+      </c>
+      <c r="N351" t="inlineStr">
+        <is>
+          <t>-36.799887528646714,175.7236950124138</t>
+        </is>
+      </c>
+      <c r="O351" t="inlineStr">
+        <is>
+          <t>-36.80061215829349,175.72368358901932</t>
+        </is>
+      </c>
+      <c r="P351" t="inlineStr">
+        <is>
+          <t>-36.80132705251034,175.723709574643</t>
+        </is>
+      </c>
+      <c r="Q351" t="inlineStr">
+        <is>
+          <t>-36.80203723102088,175.7237200059837</t>
+        </is>
+      </c>
+      <c r="R351" t="inlineStr">
+        <is>
+          <t>-36.802744393791706,175.72381430529546</t>
+        </is>
+      </c>
+      <c r="S351" t="inlineStr">
+        <is>
+          <t>-36.8034311023085,175.7239730721628</t>
+        </is>
+      </c>
+      <c r="T351" t="inlineStr">
+        <is>
+          <t>-36.80414928328314,175.7240642836874</t>
+        </is>
+      </c>
+      <c r="U351" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0175/nzd0175.xlsx
+++ b/data/nzd0175/nzd0175.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U351"/>
+  <dimension ref="A1:U352"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24671,6 +24671,75 @@
         <v>366.21</v>
       </c>
       <c r="U351" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-14 22:05:26+00:00</t>
+        </is>
+      </c>
+      <c r="B352" t="n">
+        <v>319.76</v>
+      </c>
+      <c r="C352" t="n">
+        <v>304.43</v>
+      </c>
+      <c r="D352" t="n">
+        <v>297.57</v>
+      </c>
+      <c r="E352" t="n">
+        <v>318.56</v>
+      </c>
+      <c r="F352" t="n">
+        <v>297.97</v>
+      </c>
+      <c r="G352" t="n">
+        <v>294.68</v>
+      </c>
+      <c r="H352" t="n">
+        <v>300.24</v>
+      </c>
+      <c r="I352" t="n">
+        <v>311.99</v>
+      </c>
+      <c r="J352" t="n">
+        <v>321.69</v>
+      </c>
+      <c r="K352" t="n">
+        <v>325.9</v>
+      </c>
+      <c r="L352" t="n">
+        <v>329.93</v>
+      </c>
+      <c r="M352" t="n">
+        <v>346.31</v>
+      </c>
+      <c r="N352" t="n">
+        <v>355.59</v>
+      </c>
+      <c r="O352" t="n">
+        <v>362.82</v>
+      </c>
+      <c r="P352" t="n">
+        <v>373.52</v>
+      </c>
+      <c r="Q352" t="n">
+        <v>371.42</v>
+      </c>
+      <c r="R352" t="n">
+        <v>378.08</v>
+      </c>
+      <c r="S352" t="n">
+        <v>378.29</v>
+      </c>
+      <c r="T352" t="n">
+        <v>365.78</v>
+      </c>
+      <c r="U352" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -24687,7 +24756,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B361"/>
+  <dimension ref="A1:B362"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28299,6 +28368,16 @@
         </is>
       </c>
       <c r="B361" t="n">
+        <v>-0.42</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>2026-03-14 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B362" t="n">
         <v>-0.42</v>
       </c>
     </row>
@@ -28468,28 +28547,28 @@
         <v>0.1008</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3388257590108897</v>
+        <v>0.3425147018560756</v>
       </c>
       <c r="J2" t="n">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="K2" t="n">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1616203100694189</v>
+        <v>0.1649421953261915</v>
       </c>
       <c r="M2" t="n">
-        <v>4.325106286647726</v>
+        <v>4.329680813451096</v>
       </c>
       <c r="N2" t="n">
-        <v>32.03923701415271</v>
+        <v>32.06431720726449</v>
       </c>
       <c r="O2" t="n">
-        <v>5.660321281884334</v>
+        <v>5.662536287500901</v>
       </c>
       <c r="P2" t="n">
-        <v>304.3049242166744</v>
+        <v>304.2650487097756</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -28546,28 +28625,28 @@
         <v>0.1504</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.07421677047954847</v>
+        <v>-0.07103247993796587</v>
       </c>
       <c r="J3" t="n">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="K3" t="n">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="L3" t="n">
-        <v>0.008901442478785215</v>
+        <v>0.008189782404503521</v>
       </c>
       <c r="M3" t="n">
-        <v>4.211654018423794</v>
+        <v>4.214215425726967</v>
       </c>
       <c r="N3" t="n">
-        <v>32.99476739233273</v>
+        <v>32.98746648358317</v>
       </c>
       <c r="O3" t="n">
-        <v>5.744107188443886</v>
+        <v>5.743471640356829</v>
       </c>
       <c r="P3" t="n">
-        <v>300.868146451985</v>
+        <v>300.8337259676383</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -28624,28 +28703,28 @@
         <v>0.1503</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.06137389741603903</v>
+        <v>-0.06365566907996396</v>
       </c>
       <c r="J4" t="n">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="K4" t="n">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="L4" t="n">
-        <v>0.007065332588072848</v>
+        <v>0.007632107545373024</v>
       </c>
       <c r="M4" t="n">
-        <v>3.972503604885362</v>
+        <v>3.973058491407657</v>
       </c>
       <c r="N4" t="n">
-        <v>28.47999981104435</v>
+        <v>28.44337911693754</v>
       </c>
       <c r="O4" t="n">
-        <v>5.336665607947002</v>
+        <v>5.333233457944395</v>
       </c>
       <c r="P4" t="n">
-        <v>303.1727903097259</v>
+        <v>303.1974550458156</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -28702,28 +28781,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.04858386109806333</v>
+        <v>-0.0473879253190123</v>
       </c>
       <c r="J5" t="n">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="K5" t="n">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="L5" t="n">
-        <v>0.009877754714854636</v>
+        <v>0.00945173433543689</v>
       </c>
       <c r="M5" t="n">
-        <v>2.691278819255225</v>
+        <v>2.690013915731135</v>
       </c>
       <c r="N5" t="n">
-        <v>12.7291424215223</v>
+        <v>12.70510675955109</v>
       </c>
       <c r="O5" t="n">
-        <v>3.567792373656615</v>
+        <v>3.564422359871384</v>
       </c>
       <c r="P5" t="n">
-        <v>317.7720085672964</v>
+        <v>317.759081138651</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -28780,28 +28859,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>0.05116642545954282</v>
+        <v>0.04905816743370868</v>
       </c>
       <c r="J6" t="n">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="K6" t="n">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="L6" t="n">
-        <v>0.008249470770334777</v>
+        <v>0.00761923502483941</v>
       </c>
       <c r="M6" t="n">
-        <v>3.199053201285746</v>
+        <v>3.196735514572945</v>
       </c>
       <c r="N6" t="n">
-        <v>16.93288740724056</v>
+        <v>16.92265116755506</v>
       </c>
       <c r="O6" t="n">
-        <v>4.114958980019189</v>
+        <v>4.113715008062063</v>
       </c>
       <c r="P6" t="n">
-        <v>300.272399369917</v>
+        <v>300.295188516017</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -28858,28 +28937,28 @@
         <v>0.0881</v>
       </c>
       <c r="I7" t="n">
-        <v>0.115870258822912</v>
+        <v>0.1159173288413783</v>
       </c>
       <c r="J7" t="n">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="K7" t="n">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="L7" t="n">
-        <v>0.03098738392032963</v>
+        <v>0.03120144630791855</v>
       </c>
       <c r="M7" t="n">
-        <v>3.844046976500309</v>
+        <v>3.833325760228576</v>
       </c>
       <c r="N7" t="n">
-        <v>22.58775065221572</v>
+        <v>22.52341703100419</v>
       </c>
       <c r="O7" t="n">
-        <v>4.752657220147032</v>
+        <v>4.745884220143195</v>
       </c>
       <c r="P7" t="n">
-        <v>291.5078097899165</v>
+        <v>291.507300988093</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -28936,28 +29015,28 @@
         <v>0.1029</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3456131991951738</v>
+        <v>0.3453987657977882</v>
       </c>
       <c r="J8" t="n">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="K8" t="n">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1644260281299088</v>
+        <v>0.1651197052626561</v>
       </c>
       <c r="M8" t="n">
-        <v>4.638795289452094</v>
+        <v>4.626527565826737</v>
       </c>
       <c r="N8" t="n">
-        <v>32.65724088111448</v>
+        <v>32.56459348297123</v>
       </c>
       <c r="O8" t="n">
-        <v>5.714651422537903</v>
+        <v>5.706539536616847</v>
       </c>
       <c r="P8" t="n">
-        <v>291.399196341972</v>
+        <v>291.4015142527599</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -29014,28 +29093,28 @@
         <v>0.1076</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2800055960503909</v>
+        <v>0.2825243285258276</v>
       </c>
       <c r="J9" t="n">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="K9" t="n">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1094649812899168</v>
+        <v>0.1116895795204254</v>
       </c>
       <c r="M9" t="n">
-        <v>4.782862056725702</v>
+        <v>4.7816518324356</v>
       </c>
       <c r="N9" t="n">
-        <v>34.31576848338717</v>
+        <v>34.27224832244455</v>
       </c>
       <c r="O9" t="n">
-        <v>5.857966241229731</v>
+        <v>5.854250449241521</v>
       </c>
       <c r="P9" t="n">
-        <v>300.1413132785657</v>
+        <v>300.1140871223427</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -29092,28 +29171,28 @@
         <v>0.1135</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1408611619258088</v>
+        <v>0.1451630452318609</v>
       </c>
       <c r="J10" t="n">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="K10" t="n">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="L10" t="n">
-        <v>0.03504934668449411</v>
+        <v>0.03717462429169338</v>
       </c>
       <c r="M10" t="n">
-        <v>4.318977447496922</v>
+        <v>4.330101845524987</v>
       </c>
       <c r="N10" t="n">
-        <v>29.38950168754306</v>
+        <v>29.46401131423787</v>
       </c>
       <c r="O10" t="n">
-        <v>5.421208508030571</v>
+        <v>5.428076207482524</v>
       </c>
       <c r="P10" t="n">
-        <v>310.4441208923488</v>
+        <v>310.3976198256076</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -29170,28 +29249,28 @@
         <v>0.2</v>
       </c>
       <c r="I11" t="n">
-        <v>0.2554649910439036</v>
+        <v>0.2572446621042296</v>
       </c>
       <c r="J11" t="n">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="K11" t="n">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1152138602825584</v>
+        <v>0.1171808338779722</v>
       </c>
       <c r="M11" t="n">
-        <v>3.879359274724271</v>
+        <v>3.876586459743742</v>
       </c>
       <c r="N11" t="n">
-        <v>27.08069464258389</v>
+        <v>27.03036422019966</v>
       </c>
       <c r="O11" t="n">
-        <v>5.203911475283173</v>
+        <v>5.199073400155037</v>
       </c>
       <c r="P11" t="n">
-        <v>315.9882223832134</v>
+        <v>315.9690028684821</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -29248,28 +29327,28 @@
         <v>0.1208</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1974930434199366</v>
+        <v>0.1978799226407544</v>
       </c>
       <c r="J12" t="n">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="K12" t="n">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="L12" t="n">
-        <v>0.05732874883036443</v>
+        <v>0.05788087374474304</v>
       </c>
       <c r="M12" t="n">
-        <v>4.609718114678083</v>
+        <v>4.59833876286293</v>
       </c>
       <c r="N12" t="n">
-        <v>34.50451410854335</v>
+        <v>34.40749047555493</v>
       </c>
       <c r="O12" t="n">
-        <v>5.874054316104282</v>
+        <v>5.865789842429997</v>
       </c>
       <c r="P12" t="n">
-        <v>323.9890380683589</v>
+        <v>323.984856110089</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -29326,28 +29405,28 @@
         <v>0.1693</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1900334351053822</v>
+        <v>0.1942090241475179</v>
       </c>
       <c r="J13" t="n">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="K13" t="n">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="L13" t="n">
-        <v>0.06198933908136051</v>
+        <v>0.06463941076080937</v>
       </c>
       <c r="M13" t="n">
-        <v>4.148663288160326</v>
+        <v>4.153351305388439</v>
       </c>
       <c r="N13" t="n">
-        <v>29.39918684302813</v>
+        <v>29.46451404991228</v>
       </c>
       <c r="O13" t="n">
-        <v>5.422101699804987</v>
+        <v>5.428122516111098</v>
       </c>
       <c r="P13" t="n">
-        <v>333.9774823530355</v>
+        <v>333.932346460005</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -29404,28 +29483,28 @@
         <v>0.2</v>
       </c>
       <c r="I14" t="n">
-        <v>0.143421323074616</v>
+        <v>0.1443784540709085</v>
       </c>
       <c r="J14" t="n">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="K14" t="n">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="L14" t="n">
-        <v>0.04050583863551216</v>
+        <v>0.04126250188476732</v>
       </c>
       <c r="M14" t="n">
-        <v>3.864227848813145</v>
+        <v>3.856633020514609</v>
       </c>
       <c r="N14" t="n">
-        <v>26.21420368152641</v>
+        <v>26.14735260674405</v>
       </c>
       <c r="O14" t="n">
-        <v>5.11998082823817</v>
+        <v>5.113448211016129</v>
       </c>
       <c r="P14" t="n">
-        <v>350.0998181429856</v>
+        <v>350.0894720668203</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -29482,28 +29561,28 @@
         <v>0.2</v>
       </c>
       <c r="I15" t="n">
-        <v>0.2258079349644337</v>
+        <v>0.2277097681004091</v>
       </c>
       <c r="J15" t="n">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="K15" t="n">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="L15" t="n">
-        <v>0.08765234936244271</v>
+        <v>0.08942626789968477</v>
       </c>
       <c r="M15" t="n">
-        <v>4.012417354171984</v>
+        <v>4.008573203555465</v>
       </c>
       <c r="N15" t="n">
-        <v>28.55352348075139</v>
+        <v>28.50310192008374</v>
       </c>
       <c r="O15" t="n">
-        <v>5.343549707895622</v>
+        <v>5.338829639544957</v>
       </c>
       <c r="P15" t="n">
-        <v>353.4910480330551</v>
+        <v>353.4704902300431</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -29560,28 +29639,28 @@
         <v>0.2</v>
       </c>
       <c r="I16" t="n">
-        <v>0.3146223192715319</v>
+        <v>0.316949523552161</v>
       </c>
       <c r="J16" t="n">
+        <v>351</v>
+      </c>
+      <c r="K16" t="n">
         <v>350</v>
       </c>
-      <c r="K16" t="n">
-        <v>349</v>
-      </c>
       <c r="L16" t="n">
-        <v>0.1737547565751607</v>
+        <v>0.1765276950629688</v>
       </c>
       <c r="M16" t="n">
-        <v>3.912908132075207</v>
+        <v>3.908731997078504</v>
       </c>
       <c r="N16" t="n">
-        <v>25.30764663571492</v>
+        <v>25.28165266359247</v>
       </c>
       <c r="O16" t="n">
-        <v>5.030670595031534</v>
+        <v>5.028086381874567</v>
       </c>
       <c r="P16" t="n">
-        <v>361.0874920126865</v>
+        <v>361.0622990098616</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -29638,28 +29717,28 @@
         <v>0.2</v>
       </c>
       <c r="I17" t="n">
-        <v>0.3835572228814936</v>
+        <v>0.3831669521773667</v>
       </c>
       <c r="J17" t="n">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="K17" t="n">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="L17" t="n">
-        <v>0.2813136187619889</v>
+        <v>0.282162149754974</v>
       </c>
       <c r="M17" t="n">
-        <v>3.455821326472964</v>
+        <v>3.448067350919309</v>
       </c>
       <c r="N17" t="n">
-        <v>20.22057499392064</v>
+        <v>20.16426888108757</v>
       </c>
       <c r="O17" t="n">
-        <v>4.496729366319553</v>
+        <v>4.490464216658181</v>
       </c>
       <c r="P17" t="n">
-        <v>361.878077700778</v>
+        <v>361.8822963191757</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -29716,28 +29795,28 @@
         <v>0.2</v>
       </c>
       <c r="I18" t="n">
-        <v>0.2989374287870309</v>
+        <v>0.3012755524907001</v>
       </c>
       <c r="J18" t="n">
+        <v>351</v>
+      </c>
+      <c r="K18" t="n">
         <v>350</v>
       </c>
-      <c r="K18" t="n">
-        <v>349</v>
-      </c>
       <c r="L18" t="n">
-        <v>0.1215923729829992</v>
+        <v>0.1238060309157414</v>
       </c>
       <c r="M18" t="n">
-        <v>4.343340524333981</v>
+        <v>4.341639101038759</v>
       </c>
       <c r="N18" t="n">
-        <v>34.37252386565712</v>
+        <v>34.32034798502025</v>
       </c>
       <c r="O18" t="n">
-        <v>5.862808530530152</v>
+        <v>5.858357106307215</v>
       </c>
       <c r="P18" t="n">
-        <v>366.0778548814452</v>
+        <v>366.0524034892542</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -29794,28 +29873,28 @@
         <v>0.1952</v>
       </c>
       <c r="I19" t="n">
-        <v>0.3718981818567377</v>
+        <v>0.3748717116092942</v>
       </c>
       <c r="J19" t="n">
+        <v>351</v>
+      </c>
+      <c r="K19" t="n">
         <v>350</v>
       </c>
-      <c r="K19" t="n">
-        <v>349</v>
-      </c>
       <c r="L19" t="n">
-        <v>0.1783110092966608</v>
+        <v>0.1812683530331568</v>
       </c>
       <c r="M19" t="n">
-        <v>4.493508826794704</v>
+        <v>4.491388719088482</v>
       </c>
       <c r="N19" t="n">
-        <v>33.93426828899536</v>
+        <v>33.91176296797727</v>
       </c>
       <c r="O19" t="n">
-        <v>5.825312720274797</v>
+        <v>5.823380716386081</v>
       </c>
       <c r="P19" t="n">
-        <v>363.2436418216609</v>
+        <v>363.2112737857845</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -29872,28 +29951,28 @@
         <v>0.2</v>
       </c>
       <c r="I20" t="n">
-        <v>0.3338629533318511</v>
+        <v>0.3363596994511966</v>
       </c>
       <c r="J20" t="n">
+        <v>351</v>
+      </c>
+      <c r="K20" t="n">
         <v>350</v>
       </c>
-      <c r="K20" t="n">
-        <v>349</v>
-      </c>
       <c r="L20" t="n">
-        <v>0.1501391620031768</v>
+        <v>0.1526650842193666</v>
       </c>
       <c r="M20" t="n">
-        <v>4.531509527782696</v>
+        <v>4.530869755600922</v>
       </c>
       <c r="N20" t="n">
-        <v>33.59319880515292</v>
+        <v>33.54970711940423</v>
       </c>
       <c r="O20" t="n">
-        <v>5.79596400999462</v>
+        <v>5.792210900804997</v>
       </c>
       <c r="P20" t="n">
-        <v>352.5747585718341</v>
+        <v>352.5475805125274</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -29931,7 +30010,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U351"/>
+  <dimension ref="A1:U352"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -67467,6 +67546,113 @@
         </is>
       </c>
     </row>
+    <row r="352">
+      <c r="A352" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-14 22:05:26+00:00</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>-36.7922103836352,175.728342620523</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>-36.792535730316246,175.72751989267312</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>-36.79293021713844,175.72674095704045</t>
+        </is>
+      </c>
+      <c r="E352" t="inlineStr">
+        <is>
+          <t>-36.793604682598506,175.7261264025129</t>
+        </is>
+      </c>
+      <c r="F352" t="inlineStr">
+        <is>
+          <t>-36.79427932615082,175.72551400500154</t>
+        </is>
+      </c>
+      <c r="G352" t="inlineStr">
+        <is>
+          <t>-36.79493374634961,175.72513764396018</t>
+        </is>
+      </c>
+      <c r="H352" t="inlineStr">
+        <is>
+          <t>-36.795621486891484,175.72485140218083</t>
+        </is>
+      </c>
+      <c r="I352" t="inlineStr">
+        <is>
+          <t>-36.79633246154492,175.72464529284028</t>
+        </is>
+      </c>
+      <c r="J352" t="inlineStr">
+        <is>
+          <t>-36.797035397029575,175.7244184761797</t>
+        </is>
+      </c>
+      <c r="K352" t="inlineStr">
+        <is>
+          <t>-36.797733664316645,175.7241446655072</t>
+        </is>
+      </c>
+      <c r="L352" t="inlineStr">
+        <is>
+          <t>-36.79844126570529,175.72392463917882</t>
+        </is>
+      </c>
+      <c r="M352" t="inlineStr">
+        <is>
+          <t>-36.79917091930167,175.72384115174478</t>
+        </is>
+      </c>
+      <c r="N352" t="inlineStr">
+        <is>
+          <t>-36.79988762060924,175.7236956747049</t>
+        </is>
+      </c>
+      <c r="O352" t="inlineStr">
+        <is>
+          <t>-36.80061195675631,175.72368068739982</t>
+        </is>
+      </c>
+      <c r="P352" t="inlineStr">
+        <is>
+          <t>-36.80132700739923,175.72370576646904</t>
+        </is>
+      </c>
+      <c r="Q352" t="inlineStr">
+        <is>
+          <t>-36.80203745017199,175.72371553354654</t>
+        </is>
+      </c>
+      <c r="R352" t="inlineStr">
+        <is>
+          <t>-36.802742862284404,175.7238300976193</t>
+        </is>
+      </c>
+      <c r="S352" t="inlineStr">
+        <is>
+          <t>-36.80343213317014,175.72396750480536</t>
+        </is>
+      </c>
+      <c r="T352" t="inlineStr">
+        <is>
+          <t>-36.804150342472205,175.72405965035162</t>
+        </is>
+      </c>
+      <c r="U352" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0175/nzd0175.xlsx
+++ b/data/nzd0175/nzd0175.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U352"/>
+  <dimension ref="A1:U354"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24742,6 +24742,144 @@
       <c r="U352" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:05:08+00:00</t>
+        </is>
+      </c>
+      <c r="B353" t="n">
+        <v>317.94</v>
+      </c>
+      <c r="C353" t="n">
+        <v>302.5</v>
+      </c>
+      <c r="D353" t="n">
+        <v>301.5</v>
+      </c>
+      <c r="E353" t="n">
+        <v>316</v>
+      </c>
+      <c r="F353" t="n">
+        <v>300.4</v>
+      </c>
+      <c r="G353" t="n">
+        <v>292.43</v>
+      </c>
+      <c r="H353" t="n">
+        <v>302.09</v>
+      </c>
+      <c r="I353" t="n">
+        <v>312.77</v>
+      </c>
+      <c r="J353" t="n">
+        <v>321.13</v>
+      </c>
+      <c r="K353" t="n">
+        <v>324.89</v>
+      </c>
+      <c r="L353" t="n">
+        <v>328.15</v>
+      </c>
+      <c r="M353" t="n">
+        <v>344.97</v>
+      </c>
+      <c r="N353" t="n">
+        <v>356.07</v>
+      </c>
+      <c r="O353" t="n">
+        <v>361.73</v>
+      </c>
+      <c r="P353" t="n">
+        <v>372.56</v>
+      </c>
+      <c r="Q353" t="n">
+        <v>367.21</v>
+      </c>
+      <c r="R353" t="n">
+        <v>376.7</v>
+      </c>
+      <c r="S353" t="n">
+        <v>373.49</v>
+      </c>
+      <c r="T353" t="n">
+        <v>365.6</v>
+      </c>
+      <c r="U353" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-25 22:04:56+00:00</t>
+        </is>
+      </c>
+      <c r="B354" t="n">
+        <v>316.38</v>
+      </c>
+      <c r="C354" t="n">
+        <v>301.18</v>
+      </c>
+      <c r="D354" t="n">
+        <v>300.5</v>
+      </c>
+      <c r="E354" t="n">
+        <v>316.35</v>
+      </c>
+      <c r="F354" t="n">
+        <v>300.82</v>
+      </c>
+      <c r="G354" t="n">
+        <v>293.34</v>
+      </c>
+      <c r="H354" t="n">
+        <v>300.62</v>
+      </c>
+      <c r="I354" t="n">
+        <v>311.06</v>
+      </c>
+      <c r="J354" t="n">
+        <v>319.54</v>
+      </c>
+      <c r="K354" t="n">
+        <v>324.1</v>
+      </c>
+      <c r="L354" t="n">
+        <v>329.29</v>
+      </c>
+      <c r="M354" t="n">
+        <v>344.48</v>
+      </c>
+      <c r="N354" t="n">
+        <v>356.61</v>
+      </c>
+      <c r="O354" t="n">
+        <v>361.95</v>
+      </c>
+      <c r="P354" t="n">
+        <v>373.08</v>
+      </c>
+      <c r="Q354" t="n">
+        <v>367.69</v>
+      </c>
+      <c r="R354" t="n">
+        <v>377.02</v>
+      </c>
+      <c r="S354" t="n">
+        <v>374.1</v>
+      </c>
+      <c r="T354" t="n">
+        <v>365.62</v>
+      </c>
+      <c r="U354" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -24756,7 +24894,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B362"/>
+  <dimension ref="A1:B364"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28379,6 +28517,26 @@
       </c>
       <c r="B362" t="n">
         <v>-0.42</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B363" t="n">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>2026-05-25 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B364" t="n">
+        <v>-0.58</v>
       </c>
     </row>
   </sheetData>
@@ -28547,28 +28705,28 @@
         <v>0.1008</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3425147018560756</v>
+        <v>0.3467641587581846</v>
       </c>
       <c r="J2" t="n">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="K2" t="n">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1649421953261915</v>
+        <v>0.1698125664751791</v>
       </c>
       <c r="M2" t="n">
-        <v>4.329680813451096</v>
+        <v>4.324501062243636</v>
       </c>
       <c r="N2" t="n">
-        <v>32.06431720726449</v>
+        <v>31.96243539170882</v>
       </c>
       <c r="O2" t="n">
-        <v>5.662536287500901</v>
+        <v>5.653533000850779</v>
       </c>
       <c r="P2" t="n">
-        <v>304.2650487097756</v>
+        <v>304.2187645317715</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -28625,28 +28783,28 @@
         <v>0.1504</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.07103247993796587</v>
+        <v>-0.06769286186841493</v>
       </c>
       <c r="J3" t="n">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="K3" t="n">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="L3" t="n">
-        <v>0.008189782404503521</v>
+        <v>0.007527178703032211</v>
       </c>
       <c r="M3" t="n">
-        <v>4.214215425726967</v>
+        <v>4.205354928662209</v>
       </c>
       <c r="N3" t="n">
-        <v>32.98746648358317</v>
+        <v>32.85014375095016</v>
       </c>
       <c r="O3" t="n">
-        <v>5.743471640356829</v>
+        <v>5.731504492796822</v>
       </c>
       <c r="P3" t="n">
-        <v>300.8337259676383</v>
+        <v>300.7973517916456</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -28703,28 +28861,28 @@
         <v>0.1503</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.06365566907996396</v>
+        <v>-0.06421426336632993</v>
       </c>
       <c r="J4" t="n">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="K4" t="n">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="L4" t="n">
-        <v>0.007632107545373024</v>
+        <v>0.007864002442658946</v>
       </c>
       <c r="M4" t="n">
-        <v>3.973058491407657</v>
+        <v>3.953520746581194</v>
       </c>
       <c r="N4" t="n">
-        <v>28.44337911693754</v>
+        <v>28.28496889918523</v>
       </c>
       <c r="O4" t="n">
-        <v>5.333233457944395</v>
+        <v>5.318361486321256</v>
       </c>
       <c r="P4" t="n">
-        <v>303.1974550458156</v>
+        <v>303.2035425427629</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -28781,28 +28939,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.0473879253190123</v>
+        <v>-0.04774843837662104</v>
       </c>
       <c r="J5" t="n">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="K5" t="n">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="L5" t="n">
-        <v>0.00945173433543689</v>
+        <v>0.009716446294209979</v>
       </c>
       <c r="M5" t="n">
-        <v>2.690013915731135</v>
+        <v>2.676377127034066</v>
       </c>
       <c r="N5" t="n">
-        <v>12.70510675955109</v>
+        <v>12.63384617949424</v>
       </c>
       <c r="O5" t="n">
-        <v>3.564422359871384</v>
+        <v>3.554412212939607</v>
       </c>
       <c r="P5" t="n">
-        <v>317.759081138651</v>
+        <v>317.7630071583361</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -28859,28 +29017,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>0.04905816743370868</v>
+        <v>0.0479122150809026</v>
       </c>
       <c r="J6" t="n">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="K6" t="n">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="L6" t="n">
-        <v>0.00761923502483941</v>
+        <v>0.007360355870492108</v>
       </c>
       <c r="M6" t="n">
-        <v>3.196735514572945</v>
+        <v>3.18229148858428</v>
       </c>
       <c r="N6" t="n">
-        <v>16.92265116755506</v>
+        <v>16.8325700563399</v>
       </c>
       <c r="O6" t="n">
-        <v>4.113715008062063</v>
+        <v>4.102751522617462</v>
       </c>
       <c r="P6" t="n">
-        <v>300.295188516017</v>
+        <v>300.3076699945787</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -28937,28 +29095,28 @@
         <v>0.0881</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1159173288413783</v>
+        <v>0.1139277883795524</v>
       </c>
       <c r="J7" t="n">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="K7" t="n">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="L7" t="n">
-        <v>0.03120144630791855</v>
+        <v>0.03052445683766425</v>
       </c>
       <c r="M7" t="n">
-        <v>3.833325760228576</v>
+        <v>3.821366879858721</v>
       </c>
       <c r="N7" t="n">
-        <v>22.52341703100419</v>
+        <v>22.4136906967853</v>
       </c>
       <c r="O7" t="n">
-        <v>4.745884220143195</v>
+        <v>4.734309949378611</v>
       </c>
       <c r="P7" t="n">
-        <v>291.507300988093</v>
+        <v>291.5289701586067</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -29015,28 +29173,28 @@
         <v>0.1029</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3453987657977882</v>
+        <v>0.3461792184984388</v>
       </c>
       <c r="J8" t="n">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="K8" t="n">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1651197052626561</v>
+        <v>0.1674943027301049</v>
       </c>
       <c r="M8" t="n">
-        <v>4.626527565826737</v>
+        <v>4.604929691776541</v>
       </c>
       <c r="N8" t="n">
-        <v>32.56459348297123</v>
+        <v>32.38577464064912</v>
       </c>
       <c r="O8" t="n">
-        <v>5.706539536616847</v>
+        <v>5.69085008066889</v>
       </c>
       <c r="P8" t="n">
-        <v>291.4015142527599</v>
+        <v>291.3930170896881</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -29093,28 +29251,28 @@
         <v>0.1076</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2825243285258276</v>
+        <v>0.2873642550426184</v>
       </c>
       <c r="J9" t="n">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="K9" t="n">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1116895795204254</v>
+        <v>0.1161032812021526</v>
       </c>
       <c r="M9" t="n">
-        <v>4.7816518324356</v>
+        <v>4.778340536957114</v>
       </c>
       <c r="N9" t="n">
-        <v>34.27224832244455</v>
+        <v>34.18122693281487</v>
       </c>
       <c r="O9" t="n">
-        <v>5.854250449241521</v>
+        <v>5.846471323184171</v>
       </c>
       <c r="P9" t="n">
-        <v>300.1140871223427</v>
+        <v>300.0613714808759</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -29171,28 +29329,28 @@
         <v>0.1135</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1451630452318609</v>
+        <v>0.1520952773790895</v>
       </c>
       <c r="J10" t="n">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="K10" t="n">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="L10" t="n">
-        <v>0.03717462429169338</v>
+        <v>0.04088740791986067</v>
       </c>
       <c r="M10" t="n">
-        <v>4.330101845524987</v>
+        <v>4.343006517531668</v>
       </c>
       <c r="N10" t="n">
-        <v>29.46401131423787</v>
+        <v>29.503707941637</v>
       </c>
       <c r="O10" t="n">
-        <v>5.428076207482524</v>
+        <v>5.431731578570226</v>
       </c>
       <c r="P10" t="n">
-        <v>310.3976198256076</v>
+        <v>310.3221127114599</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -29249,28 +29407,28 @@
         <v>0.2</v>
       </c>
       <c r="I11" t="n">
-        <v>0.2572446621042296</v>
+        <v>0.2591053182241235</v>
       </c>
       <c r="J11" t="n">
+        <v>353</v>
+      </c>
+      <c r="K11" t="n">
         <v>351</v>
       </c>
-      <c r="K11" t="n">
-        <v>349</v>
-      </c>
       <c r="L11" t="n">
-        <v>0.1171808338779722</v>
+        <v>0.1199597566725149</v>
       </c>
       <c r="M11" t="n">
-        <v>3.876586459743742</v>
+        <v>3.863154041569635</v>
       </c>
       <c r="N11" t="n">
-        <v>27.03036422019966</v>
+        <v>26.89196905113701</v>
       </c>
       <c r="O11" t="n">
-        <v>5.199073400155037</v>
+        <v>5.185746720689028</v>
       </c>
       <c r="P11" t="n">
-        <v>315.9690028684821</v>
+        <v>315.9487546446557</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -29327,28 +29485,28 @@
         <v>0.1208</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1978799226407544</v>
+        <v>0.1972175418449429</v>
       </c>
       <c r="J12" t="n">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="K12" t="n">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="L12" t="n">
-        <v>0.05788087374474304</v>
+        <v>0.05820757644570296</v>
       </c>
       <c r="M12" t="n">
-        <v>4.59833876286293</v>
+        <v>4.575771751416707</v>
       </c>
       <c r="N12" t="n">
-        <v>34.40749047555493</v>
+        <v>34.21620868052428</v>
       </c>
       <c r="O12" t="n">
-        <v>5.865789842429997</v>
+        <v>5.849462255671394</v>
       </c>
       <c r="P12" t="n">
-        <v>323.984856110089</v>
+        <v>323.9920681277088</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -29405,28 +29563,28 @@
         <v>0.1693</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1942090241475179</v>
+        <v>0.2006163244049284</v>
       </c>
       <c r="J13" t="n">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="K13" t="n">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="L13" t="n">
-        <v>0.06463941076080937</v>
+        <v>0.06911813177719961</v>
       </c>
       <c r="M13" t="n">
-        <v>4.153351305388439</v>
+        <v>4.155143616863716</v>
       </c>
       <c r="N13" t="n">
-        <v>29.46451404991228</v>
+        <v>29.47136470184412</v>
       </c>
       <c r="O13" t="n">
-        <v>5.428122516111098</v>
+        <v>5.428753512717641</v>
       </c>
       <c r="P13" t="n">
-        <v>333.932346460005</v>
+        <v>333.8625542544519</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -29483,28 +29641,28 @@
         <v>0.2</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1443784540709085</v>
+        <v>0.1471068311355117</v>
       </c>
       <c r="J14" t="n">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="K14" t="n">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="L14" t="n">
-        <v>0.04126250188476732</v>
+        <v>0.04324537085682645</v>
       </c>
       <c r="M14" t="n">
-        <v>3.856633020514609</v>
+        <v>3.844294686781926</v>
       </c>
       <c r="N14" t="n">
-        <v>26.14735260674405</v>
+        <v>26.03105412131514</v>
       </c>
       <c r="O14" t="n">
-        <v>5.113448211016129</v>
+        <v>5.102063712000777</v>
       </c>
       <c r="P14" t="n">
-        <v>350.0894720668203</v>
+        <v>350.0597508279843</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -29561,28 +29719,28 @@
         <v>0.2</v>
       </c>
       <c r="I15" t="n">
-        <v>0.2277097681004091</v>
+        <v>0.2303011653709429</v>
       </c>
       <c r="J15" t="n">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="K15" t="n">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="L15" t="n">
-        <v>0.08942626789968477</v>
+        <v>0.09226877001832801</v>
       </c>
       <c r="M15" t="n">
-        <v>4.008573203555465</v>
+        <v>3.996003038876476</v>
       </c>
       <c r="N15" t="n">
-        <v>28.50310192008374</v>
+        <v>28.37003981453854</v>
       </c>
       <c r="O15" t="n">
-        <v>5.338829639544957</v>
+        <v>5.326353331740069</v>
       </c>
       <c r="P15" t="n">
-        <v>353.4704902300431</v>
+        <v>353.4422620027921</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -29639,28 +29797,28 @@
         <v>0.2</v>
       </c>
       <c r="I16" t="n">
-        <v>0.316949523552161</v>
+        <v>0.3206872078179483</v>
       </c>
       <c r="J16" t="n">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="K16" t="n">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1765276950629688</v>
+        <v>0.1815049113599424</v>
       </c>
       <c r="M16" t="n">
-        <v>3.908731997078504</v>
+        <v>3.897472156940857</v>
       </c>
       <c r="N16" t="n">
-        <v>25.28165266359247</v>
+        <v>25.19738617945352</v>
       </c>
       <c r="O16" t="n">
-        <v>5.028086381874567</v>
+        <v>5.019699809695149</v>
       </c>
       <c r="P16" t="n">
-        <v>361.0622990098616</v>
+        <v>361.0215228191531</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -29717,28 +29875,28 @@
         <v>0.2</v>
       </c>
       <c r="I17" t="n">
-        <v>0.3831669521773667</v>
+        <v>0.377754469046123</v>
       </c>
       <c r="J17" t="n">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="K17" t="n">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="L17" t="n">
-        <v>0.282162149754974</v>
+        <v>0.277760867783407</v>
       </c>
       <c r="M17" t="n">
-        <v>3.448067350919309</v>
+        <v>3.457273073011256</v>
       </c>
       <c r="N17" t="n">
-        <v>20.16426888108757</v>
+        <v>20.17410632097793</v>
       </c>
       <c r="O17" t="n">
-        <v>4.490464216658181</v>
+        <v>4.491559453127381</v>
       </c>
       <c r="P17" t="n">
-        <v>361.8822963191757</v>
+        <v>361.9412522176549</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -29795,28 +29953,28 @@
         <v>0.2</v>
       </c>
       <c r="I18" t="n">
-        <v>0.3012755524907001</v>
+        <v>0.3044304401322776</v>
       </c>
       <c r="J18" t="n">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="K18" t="n">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="L18" t="n">
-        <v>0.1238060309157414</v>
+        <v>0.1273716891636756</v>
       </c>
       <c r="M18" t="n">
-        <v>4.341639101038759</v>
+        <v>4.331099465560666</v>
       </c>
       <c r="N18" t="n">
-        <v>34.32034798502025</v>
+        <v>34.16688398136353</v>
       </c>
       <c r="O18" t="n">
-        <v>5.858357106307215</v>
+        <v>5.845244561296262</v>
       </c>
       <c r="P18" t="n">
-        <v>366.0524034892542</v>
+        <v>366.0177980027045</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -29873,28 +30031,28 @@
         <v>0.1952</v>
       </c>
       <c r="I19" t="n">
-        <v>0.3748717116092942</v>
+        <v>0.3754781839581883</v>
       </c>
       <c r="J19" t="n">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="K19" t="n">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="L19" t="n">
-        <v>0.1812683530331568</v>
+        <v>0.1836588871748829</v>
       </c>
       <c r="M19" t="n">
-        <v>4.491388719088482</v>
+        <v>4.468016983489457</v>
       </c>
       <c r="N19" t="n">
-        <v>33.91176296797727</v>
+        <v>33.72111834549719</v>
       </c>
       <c r="O19" t="n">
-        <v>5.823380716386081</v>
+        <v>5.80698875024717</v>
       </c>
       <c r="P19" t="n">
-        <v>363.2112737857845</v>
+        <v>363.2046199567045</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -29951,28 +30109,28 @@
         <v>0.2</v>
       </c>
       <c r="I20" t="n">
-        <v>0.3363596994511966</v>
+        <v>0.3410329451169717</v>
       </c>
       <c r="J20" t="n">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="K20" t="n">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="L20" t="n">
-        <v>0.1526650842193666</v>
+        <v>0.1576099128513654</v>
       </c>
       <c r="M20" t="n">
-        <v>4.530869755600922</v>
+        <v>4.527662620876976</v>
       </c>
       <c r="N20" t="n">
-        <v>33.54970711940423</v>
+        <v>33.44993061541224</v>
       </c>
       <c r="O20" t="n">
-        <v>5.792210900804997</v>
+        <v>5.783591497971848</v>
       </c>
       <c r="P20" t="n">
-        <v>352.5475805125274</v>
+        <v>352.4963216756356</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -30010,7 +30168,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U352"/>
+  <dimension ref="A1:U354"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -67653,6 +67811,220 @@
         </is>
       </c>
     </row>
+    <row r="353">
+      <c r="A353" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:05:08+00:00</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>-36.792197499696236,175.72833001435137</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>-36.792522067609276,175.72750652462722</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>-36.79295744115394,175.7267690957534</t>
+        </is>
+      </c>
+      <c r="E353" t="inlineStr">
+        <is>
+          <t>-36.79359148855357,175.72610288574282</t>
+        </is>
+      </c>
+      <c r="F353" t="inlineStr">
+        <is>
+          <t>-36.794287272530596,175.725539365961</t>
+        </is>
+      </c>
+      <c r="G353" t="inlineStr">
+        <is>
+          <t>-36.79492638854006,175.72511416141162</t>
+        </is>
+      </c>
+      <c r="H353" t="inlineStr">
+        <is>
+          <t>-36.79562740003127,175.7248707755539</t>
+        </is>
+      </c>
+      <c r="I353" t="inlineStr">
+        <is>
+          <t>-36.79633489675298,175.72465348811048</t>
+        </is>
+      </c>
+      <c r="J353" t="inlineStr">
+        <is>
+          <t>-36.79703368949453,175.72441257383602</t>
+        </is>
+      </c>
+      <c r="K353" t="inlineStr">
+        <is>
+          <t>-36.79773092828496,175.724133875957</t>
+        </is>
+      </c>
+      <c r="L353" t="inlineStr">
+        <is>
+          <t>-36.79843692383291,175.72390544573994</t>
+        </is>
+      </c>
+      <c r="M353" t="inlineStr">
+        <is>
+          <t>-36.79916775687623,175.72382666612515</t>
+        </is>
+      </c>
+      <c r="N353" t="inlineStr">
+        <is>
+          <t>-36.799888356309246,175.72370097303394</t>
+        </is>
+      </c>
+      <c r="O353" t="inlineStr">
+        <is>
+          <t>-36.80061111184971,175.7236685229183</t>
+        </is>
+      </c>
+      <c r="P353" t="inlineStr">
+        <is>
+          <t>-36.801326880026004,175.72369501397785</t>
+        </is>
+      </c>
+      <c r="Q353" t="inlineStr">
+        <is>
+          <t>-36.802039756727225,175.72366846114343</t>
+        </is>
+      </c>
+      <c r="R353" t="inlineStr">
+        <is>
+          <t>-36.80274435065069,175.72381475014967</t>
+        </is>
+      </c>
+      <c r="S353" t="inlineStr">
+        <is>
+          <t>-36.80344183538491,175.7239151061391</t>
+        </is>
+      </c>
+      <c r="T353" t="inlineStr">
+        <is>
+          <t>-36.80415078585363,175.72405771081563</t>
+        </is>
+      </c>
+      <c r="U353" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-25 22:04:56+00:00</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>-36.79218645631874,175.72831920906484</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>-36.79251272316618,175.7274973817178</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>-36.792950513924254,175.72676193577365</t>
+        </is>
+      </c>
+      <c r="E354" t="inlineStr">
+        <is>
+          <t>-36.79359329242719,175.72610610092576</t>
+        </is>
+      </c>
+      <c r="F354" t="inlineStr">
+        <is>
+          <t>-36.7942886459784,175.7255437493372</t>
+        </is>
+      </c>
+      <c r="G354" t="inlineStr">
+        <is>
+          <t>-36.794929364365835,175.7251236587974</t>
+        </is>
+      </c>
+      <c r="H354" t="inlineStr">
+        <is>
+          <t>-36.79562270148263,175.72485538157616</t>
+        </is>
+      </c>
+      <c r="I354" t="inlineStr">
+        <is>
+          <t>-36.796329558026834,175.7246355215572</t>
+        </is>
+      </c>
+      <c r="J354" t="inlineStr">
+        <is>
+          <t>-36.797028841313036,175.72439581539723</t>
+        </is>
+      </c>
+      <c r="K354" t="inlineStr">
+        <is>
+          <t>-36.797728788219885,175.72412543660636</t>
+        </is>
+      </c>
+      <c r="L354" t="inlineStr">
+        <is>
+          <t>-36.79843970458301,175.72391773816688</t>
+        </is>
+      </c>
+      <c r="M354" t="inlineStr">
+        <is>
+          <t>-36.799166600466485,175.72382136914507</t>
+        </is>
+      </c>
+      <c r="N354" t="inlineStr">
+        <is>
+          <t>-36.799889183971466,175.7237069336542</t>
+        </is>
+      </c>
+      <c r="O354" t="inlineStr">
+        <is>
+          <t>-36.80061128238141,175.72367097813472</t>
+        </is>
+      </c>
+      <c r="P354" t="inlineStr">
+        <is>
+          <t>-36.80132694901996,175.72370083824393</t>
+        </is>
+      </c>
+      <c r="Q354" t="inlineStr">
+        <is>
+          <t>-36.80203949374799,175.72367382806846</t>
+        </is>
+      </c>
+      <c r="R354" t="inlineStr">
+        <is>
+          <t>-36.802744005522456,175.72381830898328</t>
+        </is>
+      </c>
+      <c r="S354" t="inlineStr">
+        <is>
+          <t>-36.803440602396364,175.72392176513708</t>
+        </is>
+      </c>
+      <c r="T354" t="inlineStr">
+        <is>
+          <t>-36.80415073658903,175.72405792631963</t>
+        </is>
+      </c>
+      <c r="U354" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0175/nzd0175.xlsx
+++ b/data/nzd0175/nzd0175.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U354"/>
+  <dimension ref="A1:U356"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24878,6 +24878,144 @@
         <v>365.62</v>
       </c>
       <c r="U354" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:05:18+00:00</t>
+        </is>
+      </c>
+      <c r="B355" t="n">
+        <v>316.38</v>
+      </c>
+      <c r="C355" t="n">
+        <v>301.18</v>
+      </c>
+      <c r="D355" t="n">
+        <v>300.5</v>
+      </c>
+      <c r="E355" t="n">
+        <v>316.35</v>
+      </c>
+      <c r="F355" t="n">
+        <v>301.98</v>
+      </c>
+      <c r="G355" t="n">
+        <v>294.51</v>
+      </c>
+      <c r="H355" t="n">
+        <v>301.94</v>
+      </c>
+      <c r="I355" t="n">
+        <v>311.87</v>
+      </c>
+      <c r="J355" t="n">
+        <v>320.25</v>
+      </c>
+      <c r="K355" t="n">
+        <v>324.47</v>
+      </c>
+      <c r="L355" t="n">
+        <v>330.55</v>
+      </c>
+      <c r="M355" t="n">
+        <v>345.13</v>
+      </c>
+      <c r="N355" t="n">
+        <v>357.46</v>
+      </c>
+      <c r="O355" t="n">
+        <v>362.37</v>
+      </c>
+      <c r="P355" t="n">
+        <v>373.02</v>
+      </c>
+      <c r="Q355" t="n">
+        <v>368.75</v>
+      </c>
+      <c r="R355" t="n">
+        <v>378.19</v>
+      </c>
+      <c r="S355" t="n">
+        <v>374.42</v>
+      </c>
+      <c r="T355" t="n">
+        <v>366.36</v>
+      </c>
+      <c r="U355" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-26 22:05:30+00:00</t>
+        </is>
+      </c>
+      <c r="B356" t="n">
+        <v>313.99</v>
+      </c>
+      <c r="C356" t="n">
+        <v>299.73</v>
+      </c>
+      <c r="D356" t="n">
+        <v>298.83</v>
+      </c>
+      <c r="E356" t="n">
+        <v>315.83</v>
+      </c>
+      <c r="F356" t="n">
+        <v>301.04</v>
+      </c>
+      <c r="G356" t="n">
+        <v>293.5</v>
+      </c>
+      <c r="H356" t="n">
+        <v>299.7</v>
+      </c>
+      <c r="I356" t="n">
+        <v>309.71</v>
+      </c>
+      <c r="J356" t="n">
+        <v>318.57</v>
+      </c>
+      <c r="K356" t="n">
+        <v>322.25</v>
+      </c>
+      <c r="L356" t="n">
+        <v>330.78</v>
+      </c>
+      <c r="M356" t="n">
+        <v>343.55</v>
+      </c>
+      <c r="N356" t="n">
+        <v>357.77</v>
+      </c>
+      <c r="O356" t="n">
+        <v>362.57</v>
+      </c>
+      <c r="P356" t="n">
+        <v>373.09</v>
+      </c>
+      <c r="Q356" t="n">
+        <v>368.82</v>
+      </c>
+      <c r="R356" t="n">
+        <v>378.35</v>
+      </c>
+      <c r="S356" t="n">
+        <v>374.73</v>
+      </c>
+      <c r="T356" t="n">
+        <v>366.5</v>
+      </c>
+      <c r="U356" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -24894,7 +25032,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B364"/>
+  <dimension ref="A1:B366"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28537,6 +28675,26 @@
       </c>
       <c r="B364" t="n">
         <v>-0.58</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B365" t="n">
+        <v>-0.55</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>2026-06-26 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B366" t="n">
+        <v>-0.67</v>
       </c>
     </row>
   </sheetData>
@@ -28705,28 +28863,28 @@
         <v>0.1008</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3467641587581846</v>
+        <v>0.3486143472292855</v>
       </c>
       <c r="J2" t="n">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="K2" t="n">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1698125664751791</v>
+        <v>0.1730195951825623</v>
       </c>
       <c r="M2" t="n">
-        <v>4.324501062243636</v>
+        <v>4.308538351364213</v>
       </c>
       <c r="N2" t="n">
-        <v>31.96243539170882</v>
+        <v>31.80530847775505</v>
       </c>
       <c r="O2" t="n">
-        <v>5.653533000850779</v>
+        <v>5.639619533067373</v>
       </c>
       <c r="P2" t="n">
-        <v>304.2187645317715</v>
+        <v>304.1985610841822</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -28783,28 +28941,28 @@
         <v>0.1504</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.06769286186841493</v>
+        <v>-0.06601484531676112</v>
       </c>
       <c r="J3" t="n">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="K3" t="n">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="L3" t="n">
-        <v>0.007527178703032211</v>
+        <v>0.007248511842765426</v>
       </c>
       <c r="M3" t="n">
-        <v>4.205354928662209</v>
+        <v>4.189240234638918</v>
       </c>
       <c r="N3" t="n">
-        <v>32.85014375095016</v>
+        <v>32.68015332412971</v>
       </c>
       <c r="O3" t="n">
-        <v>5.731504492796822</v>
+        <v>5.71665578149758</v>
       </c>
       <c r="P3" t="n">
-        <v>300.7973517916456</v>
+        <v>300.7790242743171</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -28861,28 +29019,28 @@
         <v>0.1503</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.06421426336632993</v>
+        <v>-0.06627033351980929</v>
       </c>
       <c r="J4" t="n">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="K4" t="n">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="L4" t="n">
-        <v>0.007864002442658946</v>
+        <v>0.008470530206213023</v>
       </c>
       <c r="M4" t="n">
-        <v>3.953520746581194</v>
+        <v>3.941735655011681</v>
       </c>
       <c r="N4" t="n">
-        <v>28.28496889918523</v>
+        <v>28.14767417392079</v>
       </c>
       <c r="O4" t="n">
-        <v>5.318361486321256</v>
+        <v>5.305438169832987</v>
       </c>
       <c r="P4" t="n">
-        <v>303.2035425427629</v>
+        <v>303.226018480239</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -28939,28 +29097,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.04774843837662104</v>
+        <v>-0.04818964902624645</v>
       </c>
       <c r="J5" t="n">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="K5" t="n">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="L5" t="n">
-        <v>0.009716446294209979</v>
+        <v>0.01001889845213166</v>
       </c>
       <c r="M5" t="n">
-        <v>2.676377127034066</v>
+        <v>2.663230322879148</v>
       </c>
       <c r="N5" t="n">
-        <v>12.63384617949424</v>
+        <v>12.56387559234889</v>
       </c>
       <c r="O5" t="n">
-        <v>3.554412212939607</v>
+        <v>3.544555767984034</v>
       </c>
       <c r="P5" t="n">
-        <v>317.7630071583361</v>
+        <v>317.7678311244414</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -29017,28 +29175,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0479122150809026</v>
+        <v>0.04781129328422732</v>
       </c>
       <c r="J6" t="n">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="K6" t="n">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="L6" t="n">
-        <v>0.007360355870492108</v>
+        <v>0.007421719000070492</v>
       </c>
       <c r="M6" t="n">
-        <v>3.18229148858428</v>
+        <v>3.166846247033047</v>
       </c>
       <c r="N6" t="n">
-        <v>16.8325700563399</v>
+        <v>16.73903491258167</v>
       </c>
       <c r="O6" t="n">
-        <v>4.102751522617462</v>
+        <v>4.091336567991158</v>
       </c>
       <c r="P6" t="n">
-        <v>300.3076699945787</v>
+        <v>300.3087780420874</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -29095,28 +29253,28 @@
         <v>0.0881</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1139277883795524</v>
+        <v>0.1132585944576712</v>
       </c>
       <c r="J7" t="n">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="K7" t="n">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="L7" t="n">
-        <v>0.03052445683766425</v>
+        <v>0.03054593619568613</v>
       </c>
       <c r="M7" t="n">
-        <v>3.821366879858721</v>
+        <v>3.803071670743236</v>
       </c>
       <c r="N7" t="n">
-        <v>22.4136906967853</v>
+        <v>22.29078187468119</v>
       </c>
       <c r="O7" t="n">
-        <v>4.734309949378611</v>
+        <v>4.721311457072197</v>
       </c>
       <c r="P7" t="n">
-        <v>291.5289701586067</v>
+        <v>291.536288087836</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -29173,28 +29331,28 @@
         <v>0.1029</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3461792184984388</v>
+        <v>0.3462995951508263</v>
       </c>
       <c r="J8" t="n">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="K8" t="n">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1674943027301049</v>
+        <v>0.1693333327401693</v>
       </c>
       <c r="M8" t="n">
-        <v>4.604929691776541</v>
+        <v>4.585381851258705</v>
       </c>
       <c r="N8" t="n">
-        <v>32.38577464064912</v>
+        <v>32.21050002169016</v>
       </c>
       <c r="O8" t="n">
-        <v>5.69085008066889</v>
+        <v>5.675429501076563</v>
       </c>
       <c r="P8" t="n">
-        <v>291.3930170896881</v>
+        <v>291.3917143163197</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -29251,28 +29409,28 @@
         <v>0.1076</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2873642550426184</v>
+        <v>0.290758933298203</v>
       </c>
       <c r="J9" t="n">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="K9" t="n">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1161032812021526</v>
+        <v>0.1196903686408657</v>
       </c>
       <c r="M9" t="n">
-        <v>4.778340536957114</v>
+        <v>4.768037436949993</v>
       </c>
       <c r="N9" t="n">
-        <v>34.18122693281487</v>
+        <v>34.0448601200686</v>
       </c>
       <c r="O9" t="n">
-        <v>5.846471323184171</v>
+        <v>5.834797350385752</v>
       </c>
       <c r="P9" t="n">
-        <v>300.0613714808759</v>
+        <v>300.0242900768182</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -29329,28 +29487,28 @@
         <v>0.1135</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1520952773790895</v>
+        <v>0.1577592983810374</v>
       </c>
       <c r="J10" t="n">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="K10" t="n">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="L10" t="n">
-        <v>0.04088740791986067</v>
+        <v>0.04418288657479641</v>
       </c>
       <c r="M10" t="n">
-        <v>4.343006517531668</v>
+        <v>4.349429138195616</v>
       </c>
       <c r="N10" t="n">
-        <v>29.503707941637</v>
+        <v>29.47948008550809</v>
       </c>
       <c r="O10" t="n">
-        <v>5.431731578570226</v>
+        <v>5.429500905747055</v>
       </c>
       <c r="P10" t="n">
-        <v>310.3221127114599</v>
+        <v>310.2602316156314</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -29407,28 +29565,28 @@
         <v>0.2</v>
       </c>
       <c r="I11" t="n">
-        <v>0.2591053182241235</v>
+        <v>0.2595985887890675</v>
       </c>
       <c r="J11" t="n">
+        <v>355</v>
+      </c>
+      <c r="K11" t="n">
         <v>353</v>
       </c>
-      <c r="K11" t="n">
-        <v>351</v>
-      </c>
       <c r="L11" t="n">
-        <v>0.1199597566725149</v>
+        <v>0.1216730643397586</v>
       </c>
       <c r="M11" t="n">
-        <v>3.863154041569635</v>
+        <v>3.847434540122679</v>
       </c>
       <c r="N11" t="n">
-        <v>26.89196905113701</v>
+        <v>26.7476954110324</v>
       </c>
       <c r="O11" t="n">
-        <v>5.185746720689028</v>
+        <v>5.171817418570806</v>
       </c>
       <c r="P11" t="n">
-        <v>315.9487546446557</v>
+        <v>315.9433817104776</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -29485,28 +29643,28 @@
         <v>0.1208</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1972175418449429</v>
+        <v>0.1987669628712726</v>
       </c>
       <c r="J12" t="n">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="K12" t="n">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="L12" t="n">
-        <v>0.05820757644570296</v>
+        <v>0.05976193947444153</v>
       </c>
       <c r="M12" t="n">
-        <v>4.575771751416707</v>
+        <v>4.557086913290258</v>
       </c>
       <c r="N12" t="n">
-        <v>34.21620868052428</v>
+        <v>34.03382168239621</v>
       </c>
       <c r="O12" t="n">
-        <v>5.849462255671394</v>
+        <v>5.833851359299121</v>
       </c>
       <c r="P12" t="n">
-        <v>323.9920681277088</v>
+        <v>323.9751364565766</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -29563,28 +29721,28 @@
         <v>0.1693</v>
       </c>
       <c r="I13" t="n">
-        <v>0.2006163244049284</v>
+        <v>0.2063792729683656</v>
       </c>
       <c r="J13" t="n">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="K13" t="n">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="L13" t="n">
-        <v>0.06911813177719961</v>
+        <v>0.07337290521738637</v>
       </c>
       <c r="M13" t="n">
-        <v>4.155143616863716</v>
+        <v>4.154833765466264</v>
       </c>
       <c r="N13" t="n">
-        <v>29.47136470184412</v>
+        <v>29.45171623097553</v>
       </c>
       <c r="O13" t="n">
-        <v>5.428753512717641</v>
+        <v>5.426943544111688</v>
       </c>
       <c r="P13" t="n">
-        <v>333.8625542544519</v>
+        <v>333.7995916262452</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -29641,28 +29799,28 @@
         <v>0.2</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1471068311355117</v>
+        <v>0.1511852896682452</v>
       </c>
       <c r="J14" t="n">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="K14" t="n">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="L14" t="n">
-        <v>0.04324537085682645</v>
+        <v>0.04599805746273622</v>
       </c>
       <c r="M14" t="n">
-        <v>3.844294686781926</v>
+        <v>3.836663283786224</v>
       </c>
       <c r="N14" t="n">
-        <v>26.03105412131514</v>
+        <v>25.95601471928554</v>
       </c>
       <c r="O14" t="n">
-        <v>5.102063712000777</v>
+        <v>5.094704576252242</v>
       </c>
       <c r="P14" t="n">
-        <v>350.0597508279843</v>
+        <v>350.0151839336756</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -29719,28 +29877,28 @@
         <v>0.2</v>
       </c>
       <c r="I15" t="n">
-        <v>0.2303011653709429</v>
+        <v>0.233511505229501</v>
       </c>
       <c r="J15" t="n">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="K15" t="n">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="L15" t="n">
-        <v>0.09226877001832801</v>
+        <v>0.09556814218176868</v>
       </c>
       <c r="M15" t="n">
-        <v>3.996003038876476</v>
+        <v>3.986007952493838</v>
       </c>
       <c r="N15" t="n">
-        <v>28.37003981453854</v>
+        <v>28.2545533422567</v>
       </c>
       <c r="O15" t="n">
-        <v>5.326353331740069</v>
+        <v>5.315501231516808</v>
       </c>
       <c r="P15" t="n">
-        <v>353.4422620027921</v>
+        <v>353.407181637038</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -29797,28 +29955,28 @@
         <v>0.2</v>
       </c>
       <c r="I16" t="n">
-        <v>0.3206872078179483</v>
+        <v>0.3245525356763171</v>
       </c>
       <c r="J16" t="n">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="K16" t="n">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1815049113599424</v>
+        <v>0.1866187989427969</v>
       </c>
       <c r="M16" t="n">
-        <v>3.897472156940857</v>
+        <v>3.886619352741398</v>
       </c>
       <c r="N16" t="n">
-        <v>25.19738617945352</v>
+        <v>25.11924328110433</v>
       </c>
       <c r="O16" t="n">
-        <v>5.019699809695149</v>
+        <v>5.0119101429599</v>
       </c>
       <c r="P16" t="n">
-        <v>361.0215228191531</v>
+        <v>360.9792229071793</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -29875,28 +30033,28 @@
         <v>0.2</v>
       </c>
       <c r="I17" t="n">
-        <v>0.377754469046123</v>
+        <v>0.3739797405012499</v>
       </c>
       <c r="J17" t="n">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="K17" t="n">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="L17" t="n">
-        <v>0.277760867783407</v>
+        <v>0.2756643548620858</v>
       </c>
       <c r="M17" t="n">
-        <v>3.457273073011256</v>
+        <v>3.457787011784612</v>
       </c>
       <c r="N17" t="n">
-        <v>20.17410632097793</v>
+        <v>20.12169530271354</v>
       </c>
       <c r="O17" t="n">
-        <v>4.491559453127381</v>
+        <v>4.48572126895035</v>
       </c>
       <c r="P17" t="n">
-        <v>361.9412522176549</v>
+        <v>361.9824982332254</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -29953,28 +30111,28 @@
         <v>0.2</v>
       </c>
       <c r="I18" t="n">
-        <v>0.3044304401322776</v>
+        <v>0.3090794579848619</v>
       </c>
       <c r="J18" t="n">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="K18" t="n">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="L18" t="n">
-        <v>0.1273716891636756</v>
+        <v>0.1319236892837969</v>
       </c>
       <c r="M18" t="n">
-        <v>4.331099465560666</v>
+        <v>4.327190576915353</v>
       </c>
       <c r="N18" t="n">
-        <v>34.16688398136353</v>
+        <v>34.06535402906487</v>
       </c>
       <c r="O18" t="n">
-        <v>5.845244561296262</v>
+        <v>5.83655326618929</v>
       </c>
       <c r="P18" t="n">
-        <v>366.0177980027045</v>
+        <v>365.9666457566711</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -30031,28 +30189,28 @@
         <v>0.1952</v>
       </c>
       <c r="I19" t="n">
-        <v>0.3754781839581883</v>
+        <v>0.3769227817199275</v>
       </c>
       <c r="J19" t="n">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="K19" t="n">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="L19" t="n">
-        <v>0.1836588871748829</v>
+        <v>0.1866970327921845</v>
       </c>
       <c r="M19" t="n">
-        <v>4.468016983489457</v>
+        <v>4.447819131726618</v>
       </c>
       <c r="N19" t="n">
-        <v>33.72111834549719</v>
+        <v>33.53954929754952</v>
       </c>
       <c r="O19" t="n">
-        <v>5.80698875024717</v>
+        <v>5.79133398255959</v>
       </c>
       <c r="P19" t="n">
-        <v>363.2046199567045</v>
+        <v>363.1887239588044</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -30109,28 +30267,28 @@
         <v>0.2</v>
       </c>
       <c r="I20" t="n">
-        <v>0.3410329451169717</v>
+        <v>0.3464748323205785</v>
       </c>
       <c r="J20" t="n">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="K20" t="n">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="L20" t="n">
-        <v>0.1576099128513654</v>
+        <v>0.16307866065399</v>
       </c>
       <c r="M20" t="n">
-        <v>4.527662620876976</v>
+        <v>4.52800196248611</v>
       </c>
       <c r="N20" t="n">
-        <v>33.44993061541224</v>
+        <v>33.38630818400213</v>
       </c>
       <c r="O20" t="n">
-        <v>5.783591497971848</v>
+        <v>5.778088627219396</v>
       </c>
       <c r="P20" t="n">
-        <v>352.4963216756356</v>
+        <v>352.4364458783259</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -30168,7 +30326,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U354"/>
+  <dimension ref="A1:U356"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -68025,6 +68183,220 @@
         </is>
       </c>
     </row>
+    <row r="355">
+      <c r="A355" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:05:18+00:00</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>-36.79218645631874,175.72831920906484</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>-36.79251272316618,175.7274973817178</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>-36.792950513924254,175.72676193577365</t>
+        </is>
+      </c>
+      <c r="E355" t="inlineStr">
+        <is>
+          <t>-36.79359329242719,175.72610610092576</t>
+        </is>
+      </c>
+      <c r="F355" t="inlineStr">
+        <is>
+          <t>-36.7942924393095,175.72555585580557</t>
+        </is>
+      </c>
+      <c r="G355" t="inlineStr">
+        <is>
+          <t>-36.79493319042639,175.725135869723</t>
+        </is>
+      </c>
+      <c r="H355" t="inlineStr">
+        <is>
+          <t>-36.79562692058763,175.72486920473978</t>
+        </is>
+      </c>
+      <c r="I355" t="inlineStr">
+        <is>
+          <t>-36.79633208689747,175.72464403202952</t>
+        </is>
+      </c>
+      <c r="J355" t="inlineStr">
+        <is>
+          <t>-36.79703100622457,175.72440329872498</t>
+        </is>
+      </c>
+      <c r="K355" t="inlineStr">
+        <is>
+          <t>-36.79772979052892,175.72412938921357</t>
+        </is>
+      </c>
+      <c r="L355" t="inlineStr">
+        <is>
+          <t>-36.798442778042116,175.72393132453442</t>
+        </is>
+      </c>
+      <c r="M355" t="inlineStr">
+        <is>
+          <t>-36.799168134479366,175.72382839575133</t>
+        </is>
+      </c>
+      <c r="N355" t="inlineStr">
+        <is>
+          <t>-36.79989048677247,175.72371631611222</t>
+        </is>
+      </c>
+      <c r="O355" t="inlineStr">
+        <is>
+          <t>-36.80061160794181,175.72367566536616</t>
+        </is>
+      </c>
+      <c r="P355" t="inlineStr">
+        <is>
+          <t>-36.80132694105914,175.7237001662132</t>
+        </is>
+      </c>
+      <c r="Q355" t="inlineStr">
+        <is>
+          <t>-36.80203891300133,175.7236856800277</t>
+        </is>
+      </c>
+      <c r="R355" t="inlineStr">
+        <is>
+          <t>-36.80274274364642,175.72383132096832</t>
+        </is>
+      </c>
+      <c r="S355" t="inlineStr">
+        <is>
+          <t>-36.80343995558257,175.72392525838183</t>
+        </is>
+      </c>
+      <c r="T355" t="inlineStr">
+        <is>
+          <t>-36.80414891379855,175.72406589996731</t>
+        </is>
+      </c>
+      <c r="U355" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-26 22:05:30+00:00</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>-36.792169537295926,175.72830265481784</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>-36.79250245843612,175.7274873383729</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>-36.79293894544958,175.72674997861034</t>
+        </is>
+      </c>
+      <c r="E356" t="inlineStr">
+        <is>
+          <t>-36.79359061238635,175.7261013240826</t>
+        </is>
+      </c>
+      <c r="F356" t="inlineStr">
+        <is>
+          <t>-36.79428936540336,175.72554604539147</t>
+        </is>
+      </c>
+      <c r="G356" t="inlineStr">
+        <is>
+          <t>-36.79492988758787,175.72512532866753</t>
+        </is>
+      </c>
+      <c r="H356" t="inlineStr">
+        <is>
+          <t>-36.79561976089331,175.72484574725087</t>
+        </is>
+      </c>
+      <c r="I356" t="inlineStr">
+        <is>
+          <t>-36.796325343241065,175.72462133743784</t>
+        </is>
+      </c>
+      <c r="J356" t="inlineStr">
+        <is>
+          <t>-36.79702588361619,175.72438559169657</t>
+        </is>
+      </c>
+      <c r="K356" t="inlineStr">
+        <is>
+          <t>-36.79772377667263,175.72410567357176</t>
+        </is>
+      </c>
+      <c r="L356" t="inlineStr">
+        <is>
+          <t>-36.79844333907018,175.72393380458576</t>
+        </is>
+      </c>
+      <c r="M356" t="inlineStr">
+        <is>
+          <t>-36.79916440564729,175.72381131569355</t>
+        </is>
+      </c>
+      <c r="N356" t="inlineStr">
+        <is>
+          <t>-36.79989096191149,175.72371973794992</t>
+        </is>
+      </c>
+      <c r="O356" t="inlineStr">
+        <is>
+          <t>-36.80061176297051,175.7236778973811</t>
+        </is>
+      </c>
+      <c r="P356" t="inlineStr">
+        <is>
+          <t>-36.80132695034675,175.72370095024905</t>
+        </is>
+      </c>
+      <c r="Q356" t="inlineStr">
+        <is>
+          <t>-36.802038874650094,175.72368646270425</t>
+        </is>
+      </c>
+      <c r="R356" t="inlineStr">
+        <is>
+          <t>-36.802742571082064,175.72383310038504</t>
+        </is>
+      </c>
+      <c r="S356" t="inlineStr">
+        <is>
+          <t>-36.8034393289816,175.72392864246262</t>
+        </is>
+      </c>
+      <c r="T356" t="inlineStr">
+        <is>
+          <t>-36.804148568946225,175.72406740849522</t>
+        </is>
+      </c>
+      <c r="U356" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
